--- a/Doc/ConfigPrj/ExcelCfg/STM32H753ZI/STM32H753ZI_HwCfg.xlsx
+++ b/Doc/ConfigPrj/ExcelCfg/STM32H753ZI/STM32H753ZI_HwCfg.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Software\STM32\fIntegration_H7\Doc\ConfigPrj\ExcelCfg\STM32H753ZI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC320765-4CCA-4C9D-ADCB-900292E39A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E59605E-7BF5-4A39-8D32-0266019849BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{2AF09063-600F-437A-B138-F66136E922A5}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{2AF09063-600F-437A-B138-F66136E922A5}"/>
   </bookViews>
   <sheets>
     <sheet name="General_Info" sheetId="1" r:id="rId1"/>

--- a/Doc/ConfigPrj/ExcelCfg/STM32H753ZI/STM32H753ZI_HwCfg.xlsx
+++ b/Doc/ConfigPrj/ExcelCfg/STM32H753ZI/STM32H753ZI_HwCfg.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Software\STM32\fIntegration_H7\Doc\ConfigPrj\ExcelCfg\STM32H753ZI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROJECT\STM32\H7_Integration\Doc\ConfigPrj\ExcelCfg\STM32H753ZI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E59605E-7BF5-4A39-8D32-0266019849BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17BBC91F-5E89-4159-AD20-07899E094710}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{2AF09063-600F-437A-B138-F66136E922A5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{2AF09063-600F-437A-B138-F66136E922A5}"/>
   </bookViews>
   <sheets>
     <sheet name="General_Info" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1387" uniqueCount="571">
   <si>
     <t>Colonne1</t>
   </si>
@@ -578,9 +578,6 @@
     <t>TIMER_4</t>
   </si>
   <si>
-    <t>TIMER_8</t>
-  </si>
-  <si>
     <t>TIMER_5</t>
   </si>
   <si>
@@ -827,51 +824,6 @@
     <t>ADC3_IRQHandler</t>
   </si>
   <si>
-    <t>DMA2_Channel1_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA2_Channel2_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA2_Channel3_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA2_Channel4_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA2_Channel5_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA1_Channel1_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA1_Channel2_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA1_Channel3_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA1_Channel4_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA1_Channel5_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA1_Channel6_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA1_Channel7_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA2_Channel6_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA2_Channel7_IRQHandler</t>
-  </si>
-  <si>
-    <t>DMA2_Channel8_IRQHandler</t>
-  </si>
-  <si>
     <t>F</t>
   </si>
   <si>
@@ -1709,9 +1661,6 @@
     <t>GPIO_AF2_TIM3</t>
   </si>
   <si>
-    <t>GPIO_AF3_TIM8</t>
-  </si>
-  <si>
     <t>GPIO_AF9_TIM13</t>
   </si>
   <si>
@@ -1748,7 +1697,67 @@
     <t>CHANNEL_8</t>
   </si>
   <si>
-    <t>DMA1_Channel8_IRQHandler</t>
+    <t>DMA1_Stream1_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA1_Stream2_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA1_Stream3_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA1_Stream4_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA1_Stream5_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA1_Stream6_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA1_Stream7_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA1_Stream8_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA2_Stream1_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA2_Stream2_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA2_Stream3_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA2_Stream4_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA2_Stream5_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA2_Stream6_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA2_Stream7_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA2_Stream8_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA1_Stream0_IRQHandler</t>
+  </si>
+  <si>
+    <t>DMA2_Stream0_IRQHandler</t>
+  </si>
+  <si>
+    <t>GPIO_AF7_USART3</t>
+  </si>
+  <si>
+    <t>USART3_RX</t>
+  </si>
+  <si>
+    <t>USART3_TX</t>
   </si>
 </sst>
 </file>
@@ -1895,7 +1904,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1915,8 +1924,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4451,8 +4458,8 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9F4B7C8E-8730-4908-B1BE-2954AF9427C0}" name="FMKIO_InputDig" displayName="FMKIO_InputDig" ref="A6:B27" totalsRowShown="0">
-  <autoFilter ref="A6:B27" xr:uid="{9F4B7C8E-8730-4908-B1BE-2954AF9427C0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{9F4B7C8E-8730-4908-B1BE-2954AF9427C0}" name="FMKIO_InputDig" displayName="FMKIO_InputDig" ref="A6:B25" totalsRowShown="0">
+  <autoFilter ref="A6:B25" xr:uid="{9F4B7C8E-8730-4908-B1BE-2954AF9427C0}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{6C4BEFED-5E85-401A-AA66-51A07D13FEBC}" name="GPIO_name"/>
     <tableColumn id="2" xr3:uid="{E08F986F-8D6D-4DEB-A18F-F4FB9A36C956}" name="Pin_name"/>
@@ -4462,8 +4469,8 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{098A48DC-88A9-4122-ADE1-86E0F3796141}" name="FMKIO_OutputDig" displayName="FMKIO_OutputDig" ref="AA7:AB31" totalsRowShown="0">
-  <autoFilter ref="AA7:AB31" xr:uid="{098A48DC-88A9-4122-ADE1-86E0F3796141}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{098A48DC-88A9-4122-ADE1-86E0F3796141}" name="FMKIO_OutputDig" displayName="FMKIO_OutputDig" ref="AA7:AB29" totalsRowShown="0">
+  <autoFilter ref="AA7:AB29" xr:uid="{098A48DC-88A9-4122-ADE1-86E0F3796141}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{395BD36A-0840-48CF-8D8D-56878E366FC5}" name="GPIO_name"/>
     <tableColumn id="2" xr3:uid="{34DF2CF3-8826-4F9E-A09D-280EE0FEFFBB}" name="Pin_name"/>
@@ -4499,8 +4506,8 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{DE41CD30-BCBD-40FE-B5DD-848DAAA9C25B}" name="FMKIO_OutputPwm" displayName="FMKIO_OutputPwm" ref="P6:U25" totalsRowShown="0">
-  <autoFilter ref="P6:U25" xr:uid="{DE41CD30-BCBD-40FE-B5DD-848DAAA9C25B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{DE41CD30-BCBD-40FE-B5DD-848DAAA9C25B}" name="FMKIO_OutputPwm" displayName="FMKIO_OutputPwm" ref="C52:H69" totalsRowShown="0">
+  <autoFilter ref="C52:H69" xr:uid="{DE41CD30-BCBD-40FE-B5DD-848DAAA9C25B}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{F2B685DB-87AE-429A-9E70-076DA856F9A2}" name="GPIO_name"/>
     <tableColumn id="2" xr3:uid="{30126296-E33C-4D56-9110-2D49FE159CF1}" name="Pin_name"/>
@@ -4593,8 +4600,8 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{E02B856E-D01E-4A8C-8208-1406C54C0BB0}" name="FMKIO_EcdrCfg" displayName="FMKIO_EcdrCfg" ref="K36:Q38" totalsRowShown="0">
-  <autoFilter ref="K36:Q38" xr:uid="{E02B856E-D01E-4A8C-8208-1406C54C0BB0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{E02B856E-D01E-4A8C-8208-1406C54C0BB0}" name="FMKIO_EcdrCfg" displayName="FMKIO_EcdrCfg" ref="K36:Q39" totalsRowShown="0">
+  <autoFilter ref="K36:Q39" xr:uid="{E02B856E-D01E-4A8C-8208-1406C54C0BB0}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{A26AA337-C773-4712-A268-4BC1750DF480}" name="TI1_Port"/>
     <tableColumn id="4" xr3:uid="{4AA947A3-B8F2-42ED-8CE3-C9B154A54E6F}" name="TI1_Pin"/>
@@ -4668,8 +4675,8 @@
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{333A4E38-7E7A-4098-B282-4F58DD308AC2}" name="FMKMAC_Cfg" displayName="FMKMAC_Cfg" ref="B2:E11" totalsRowShown="0">
-  <autoFilter ref="B2:E11" xr:uid="{333A4E38-7E7A-4098-B282-4F58DD308AC2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{333A4E38-7E7A-4098-B282-4F58DD308AC2}" name="FMKMAC_Cfg" displayName="FMKMAC_Cfg" ref="B2:E13" totalsRowShown="0">
+  <autoFilter ref="B2:E13" xr:uid="{333A4E38-7E7A-4098-B282-4F58DD308AC2}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{9B6EDCAA-F526-412C-A8EC-AC6897A0EB04}" name="RqstDmaType"/>
     <tableColumn id="2" xr3:uid="{ED583461-6D2B-456F-A394-15F76B273D8C}" name="DMA "/>
@@ -4681,8 +4688,8 @@
 </file>
 
 <file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{8B613F4D-88F2-4091-AA3A-5550AB627653}" name="FMKMAC_IRQN" displayName="FMKMAC_IRQN" ref="J3:K19" totalsRowShown="0">
-  <autoFilter ref="J3:K19" xr:uid="{8B613F4D-88F2-4091-AA3A-5550AB627653}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{8B613F4D-88F2-4091-AA3A-5550AB627653}" name="FMKMAC_IRQN" displayName="FMKMAC_IRQN" ref="J3:K21" totalsRowShown="0">
+  <autoFilter ref="J3:K21" xr:uid="{8B613F4D-88F2-4091-AA3A-5550AB627653}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{7FC5E369-C5C5-44CD-98EF-8136D5348789}" name="List IRQN_Handler"/>
     <tableColumn id="2" xr3:uid="{0FFD83C8-633F-48FF-B94F-239B6386B204}" name="RqstType Associated"/>
@@ -5143,51 +5150,51 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871E2D6D-43F7-44B1-8255-ECFDDA33AA9C}">
   <dimension ref="A17:AJ158"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" customWidth="1"/>
-    <col min="2" max="6" width="24.77734375" customWidth="1"/>
-    <col min="7" max="7" width="37.33203125" customWidth="1"/>
-    <col min="8" max="8" width="26.44140625" customWidth="1"/>
-    <col min="9" max="10" width="25.109375" customWidth="1"/>
-    <col min="11" max="11" width="33.109375" customWidth="1"/>
-    <col min="12" max="12" width="26.88671875" customWidth="1"/>
-    <col min="13" max="13" width="21.44140625" customWidth="1"/>
-    <col min="14" max="14" width="21.33203125" customWidth="1"/>
-    <col min="15" max="15" width="18.33203125" customWidth="1"/>
-    <col min="16" max="16" width="20.44140625" customWidth="1"/>
-    <col min="17" max="17" width="31.44140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" customWidth="1"/>
-    <col min="19" max="19" width="22.77734375" customWidth="1"/>
-    <col min="20" max="20" width="23.44140625" customWidth="1"/>
-    <col min="21" max="21" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="23.6328125" customWidth="1"/>
+    <col min="2" max="6" width="24.81640625" customWidth="1"/>
+    <col min="7" max="7" width="37.36328125" customWidth="1"/>
+    <col min="8" max="8" width="26.453125" customWidth="1"/>
+    <col min="9" max="10" width="25.08984375" customWidth="1"/>
+    <col min="11" max="11" width="33.08984375" customWidth="1"/>
+    <col min="12" max="12" width="26.90625" customWidth="1"/>
+    <col min="13" max="13" width="21.453125" customWidth="1"/>
+    <col min="14" max="14" width="21.36328125" customWidth="1"/>
+    <col min="15" max="15" width="18.36328125" customWidth="1"/>
+    <col min="16" max="16" width="20.453125" customWidth="1"/>
+    <col min="17" max="17" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.36328125" customWidth="1"/>
+    <col min="19" max="19" width="22.81640625" customWidth="1"/>
+    <col min="20" max="20" width="23.453125" customWidth="1"/>
+    <col min="21" max="21" width="20.6328125" customWidth="1"/>
     <col min="22" max="22" width="21" customWidth="1"/>
-    <col min="23" max="23" width="33.88671875" customWidth="1"/>
-    <col min="24" max="24" width="35.33203125" customWidth="1"/>
-    <col min="25" max="25" width="21.21875" customWidth="1"/>
-    <col min="26" max="26" width="19.109375" customWidth="1"/>
-    <col min="27" max="27" width="18.77734375" customWidth="1"/>
-    <col min="28" max="28" width="29.21875" customWidth="1"/>
-    <col min="30" max="30" width="17.44140625" customWidth="1"/>
+    <col min="23" max="23" width="33.90625" customWidth="1"/>
+    <col min="24" max="24" width="35.36328125" customWidth="1"/>
+    <col min="25" max="25" width="21.1796875" customWidth="1"/>
+    <col min="26" max="26" width="19.08984375" customWidth="1"/>
+    <col min="27" max="27" width="18.81640625" customWidth="1"/>
+    <col min="28" max="28" width="29.1796875" customWidth="1"/>
+    <col min="30" max="30" width="17.453125" customWidth="1"/>
     <col min="32" max="32" width="24" customWidth="1"/>
-    <col min="35" max="35" width="17.77734375" customWidth="1"/>
+    <col min="35" max="35" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H17" t="s">
-        <v>520</v>
+        <v>504</v>
       </c>
       <c r="V17" t="s">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="W17" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="X17" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.3">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>115</v>
       </c>
@@ -5195,10 +5202,10 @@
         <v>19</v>
       </c>
       <c r="I18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J18" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="L18" t="s">
         <v>54</v>
@@ -5213,13 +5220,13 @@
         <v>2</v>
       </c>
       <c r="Q18" t="s">
+        <v>182</v>
+      </c>
+      <c r="R18" t="s">
         <v>183</v>
       </c>
-      <c r="R18" t="s">
-        <v>184</v>
-      </c>
       <c r="S18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="V18" t="s">
         <v>175</v>
@@ -5231,21 +5238,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="H19" t="s">
         <v>168</v>
       </c>
       <c r="I19" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="J19" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="L19" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="M19" t="s">
         <v>65</v>
@@ -5257,24 +5264,24 @@
         <v>4</v>
       </c>
       <c r="Q19" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="R19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S19" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H20" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="I20" t="s">
-        <v>527</v>
+        <v>511</v>
       </c>
       <c r="J20" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="L20" t="s">
         <v>135</v>
@@ -5283,19 +5290,19 @@
         <v>65</v>
       </c>
       <c r="O20" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="P20">
         <v>2</v>
       </c>
       <c r="Q20" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="R20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AF20" t="s">
         <v>20</v>
@@ -5304,42 +5311,42 @@
         <v>16</v>
       </c>
       <c r="AH20" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="21" spans="1:34" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H21" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="I21" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J21" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L21" t="s">
-        <v>414</v>
+        <v>398</v>
       </c>
       <c r="M21" t="s">
         <v>65</v>
       </c>
       <c r="O21" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="P21">
         <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="R21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AF21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG21">
         <v>8</v>
@@ -5348,39 +5355,39 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H22" t="s">
-        <v>514</v>
+        <v>498</v>
       </c>
       <c r="I22" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J22" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L22" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="M22" t="s">
         <v>65</v>
       </c>
       <c r="O22" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="P22">
         <v>4</v>
       </c>
       <c r="Q22" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="R22" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AF22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG22">
         <v>8</v>
@@ -5389,18 +5396,18 @@
         <v>164</v>
       </c>
     </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H23" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="I23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J23" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L23" t="s">
-        <v>416</v>
+        <v>400</v>
       </c>
       <c r="M23" t="s">
         <v>65</v>
@@ -5412,27 +5419,27 @@
         <v>2</v>
       </c>
       <c r="Q23" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="R23" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S23" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H24" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="I24" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="J24" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L24" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="M24" t="s">
         <v>65</v>
@@ -5444,27 +5451,27 @@
         <v>1</v>
       </c>
       <c r="Q24" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="R24" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S24" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H25" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="I25" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J25" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L25" t="s">
-        <v>418</v>
+        <v>402</v>
       </c>
       <c r="M25" t="s">
         <v>65</v>
@@ -5476,27 +5483,27 @@
         <v>1</v>
       </c>
       <c r="Q25" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="R25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S25" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H26" t="s">
         <v>171</v>
       </c>
       <c r="I26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J26" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="M26" t="s">
         <v>65</v>
@@ -5511,30 +5518,30 @@
         <v>125</v>
       </c>
       <c r="R26" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S26" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B27" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H27" t="s">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="I27" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J27" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L27" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="M27" t="s">
         <v>65</v>
@@ -5549,30 +5556,30 @@
         <v>60</v>
       </c>
       <c r="R27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S27" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B28">
         <v>60</v>
       </c>
       <c r="H28" t="s">
-        <v>478</v>
+        <v>462</v>
       </c>
       <c r="I28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J28" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L28" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="M28" t="s">
         <v>65</v>
@@ -5587,13 +5594,13 @@
         <v>126</v>
       </c>
       <c r="R28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S28" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>172</v>
       </c>
@@ -5601,16 +5608,16 @@
         <v>170</v>
       </c>
       <c r="H29" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="I29" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J29" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L29" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="M29" t="s">
         <v>65</v>
@@ -5625,24 +5632,24 @@
         <v>138</v>
       </c>
       <c r="R29" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S29" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H30" t="s">
-        <v>518</v>
+        <v>502</v>
       </c>
       <c r="I30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J30" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L30" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="M30" t="s">
         <v>65</v>
@@ -5657,21 +5664,21 @@
         <v>142</v>
       </c>
       <c r="R30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S30" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H31" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
       <c r="I31" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J31" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L31" t="s">
         <v>143</v>
@@ -5686,27 +5693,27 @@
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="R31" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="S31" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.35">
       <c r="H32" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="I32" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J32" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L32" t="s">
-        <v>489</v>
+        <v>473</v>
       </c>
       <c r="M32" t="s">
         <v>65</v>
@@ -5718,78 +5725,78 @@
         <v>4</v>
       </c>
       <c r="Q32" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="R32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S32" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="33" spans="8:36" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="33" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H33" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="I33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J33" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L33" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="M33" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="34" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H34" t="s">
         <v>80</v>
       </c>
       <c r="I34" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J34" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L34" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="M34" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="35" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="35" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H35" t="s">
         <v>164</v>
       </c>
       <c r="I35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J35" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L35" t="s">
-        <v>401</v>
+        <v>385</v>
       </c>
       <c r="M35" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="36" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H36" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="I36" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="J36" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L36" t="s">
-        <v>402</v>
+        <v>386</v>
       </c>
       <c r="M36" t="s">
         <v>65</v>
@@ -5801,18 +5808,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="37" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H37" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="I37" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J37" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L37" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="M37" t="s">
         <v>65</v>
@@ -5824,52 +5831,52 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="38" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H38" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="I38" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J38" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L38" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="M38" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="39" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H39" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="I39" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J39" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L39" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="M39" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="40" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="40" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H40" t="s">
         <v>172</v>
       </c>
       <c r="I40" t="s">
-        <v>525</v>
+        <v>509</v>
       </c>
       <c r="J40" t="s">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="L40" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="M40" t="s">
         <v>65</v>
@@ -5881,27 +5888,27 @@
         <v>16</v>
       </c>
       <c r="AB40" t="s">
+        <v>188</v>
+      </c>
+      <c r="AC40" t="s">
         <v>189</v>
-      </c>
-      <c r="AC40" t="s">
-        <v>190</v>
       </c>
       <c r="AJ40" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="41" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H41" t="s">
         <v>169</v>
       </c>
       <c r="I41" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="J41" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L41" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="M41" t="s">
         <v>65</v>
@@ -5913,7 +5920,7 @@
         <v>20</v>
       </c>
       <c r="AB41" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="AC41" t="s">
         <v>168</v>
@@ -5922,30 +5929,30 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="42" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H42" t="s">
         <v>76</v>
       </c>
       <c r="I42" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J42" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L42" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="M42" t="s">
         <v>65</v>
       </c>
       <c r="Z42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AA42">
         <v>20</v>
       </c>
       <c r="AB42" t="s">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="AC42" t="s">
         <v>168</v>
@@ -5954,18 +5961,18 @@
         <v>65</v>
       </c>
     </row>
-    <row r="43" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="43" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H43" t="s">
         <v>77</v>
       </c>
       <c r="I43" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J43" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L43" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="M43" t="s">
         <v>65</v>
@@ -5977,7 +5984,7 @@
         <v>8</v>
       </c>
       <c r="Z43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AA43">
         <v>20</v>
@@ -5986,24 +5993,24 @@
         <v>135</v>
       </c>
       <c r="AC43" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="AJ43" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="44" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H44" t="s">
         <v>78</v>
       </c>
       <c r="I44" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J44" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L44" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="M44" t="s">
         <v>65</v>
@@ -6015,18 +6022,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="45" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H45" t="s">
         <v>166</v>
       </c>
       <c r="I45" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J45" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L45" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="M45" t="s">
         <v>65</v>
@@ -6038,18 +6045,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="46" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H46" t="s">
         <v>165</v>
       </c>
       <c r="I46" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J46" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L46" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="M46" t="s">
         <v>65</v>
@@ -6061,21 +6068,21 @@
         <v>16</v>
       </c>
       <c r="AJ46" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="47" spans="8:36" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H47" t="s">
         <v>79</v>
       </c>
       <c r="I47" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J47" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L47" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="M47" t="s">
         <v>65</v>
@@ -6087,47 +6094,47 @@
         <v>16</v>
       </c>
       <c r="AJ47" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="48" spans="8:36" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="48" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H48" t="s">
-        <v>487</v>
+        <v>471</v>
       </c>
       <c r="I48" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J48" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L48" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="M48" t="s">
         <v>65</v>
       </c>
       <c r="T48" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="U48">
         <v>16</v>
       </c>
       <c r="AJ48" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="49" spans="8:36" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="49" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H49" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="I49" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J49" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L49" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="M49" t="s">
         <v>65</v>
@@ -6139,224 +6146,224 @@
         <v>16</v>
       </c>
       <c r="AJ49" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="50" spans="8:36" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="50" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H50" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
       <c r="I50" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J50" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L50" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="M50" t="s">
         <v>65</v>
       </c>
       <c r="T50" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="U50">
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="51" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H51" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="I51" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J51" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L51" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s">
         <v>65</v>
       </c>
       <c r="T51" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="U51">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="52" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H52" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="I52" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J52" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L52" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="M52" t="s">
         <v>65</v>
       </c>
       <c r="AJ52" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="53" spans="8:36" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="53" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H53" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="I53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J53" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L53" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="M53" t="s">
         <v>65</v>
       </c>
       <c r="AJ53" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="54" spans="8:36" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="54" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H54" t="s">
         <v>175</v>
       </c>
       <c r="I54" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J54" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L54" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="M54" t="s">
         <v>65</v>
       </c>
       <c r="AJ54" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="55" spans="8:36" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="55" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H55" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="I55" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="J55" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L55" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="M55" t="s">
         <v>65</v>
       </c>
       <c r="AJ55" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="56" spans="8:36" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="56" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H56" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="I56" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J56" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L56" t="s">
-        <v>413</v>
+        <v>397</v>
       </c>
       <c r="M56" t="s">
         <v>65</v>
       </c>
       <c r="AJ56" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="57" spans="8:36" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="57" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H57" t="s">
         <v>155</v>
       </c>
       <c r="I57" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J57" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L57" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="M57" t="s">
         <v>65</v>
       </c>
       <c r="AJ57" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="58" spans="8:36" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="58" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H58" t="s">
         <v>154</v>
       </c>
       <c r="I58" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J58" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L58" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="M58" t="s">
         <v>65</v>
       </c>
       <c r="AJ58" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="59" spans="8:36" x14ac:dyDescent="0.3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="59" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H59" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="I59" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="J59" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L59" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="M59" t="s">
         <v>65</v>
       </c>
       <c r="AJ59" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="60" spans="8:36" x14ac:dyDescent="0.3">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="60" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H60" t="s">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="I60" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="J60" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L60" t="s">
         <v>117</v>
@@ -6365,18 +6372,18 @@
         <v>65</v>
       </c>
       <c r="AJ60" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="61" spans="8:36" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="61" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H61" t="s">
         <v>158</v>
       </c>
       <c r="I61" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J61" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L61" t="s">
         <v>118</v>
@@ -6385,18 +6392,18 @@
         <v>65</v>
       </c>
       <c r="AJ61" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="62" spans="8:36" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="62" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H62" t="s">
+        <v>427</v>
+      </c>
+      <c r="I62" t="s">
         <v>443</v>
       </c>
-      <c r="I62" t="s">
-        <v>459</v>
-      </c>
       <c r="J62" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L62" t="s">
         <v>132</v>
@@ -6405,18 +6412,18 @@
         <v>65</v>
       </c>
       <c r="AJ62" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="63" spans="8:36" x14ac:dyDescent="0.3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="63" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H63" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="I63" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="J63" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L63" t="s">
         <v>119</v>
@@ -6425,18 +6432,18 @@
         <v>65</v>
       </c>
       <c r="AJ63" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="64" spans="8:36" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="64" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H64" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="I64" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="J64" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L64" t="s">
         <v>120</v>
@@ -6445,18 +6452,18 @@
         <v>65</v>
       </c>
       <c r="AJ64" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="65" spans="8:36" x14ac:dyDescent="0.3">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="65" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H65" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="I65" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="J65" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L65" t="s">
         <v>121</v>
@@ -6465,18 +6472,18 @@
         <v>65</v>
       </c>
       <c r="AJ65" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="66" spans="8:36" x14ac:dyDescent="0.3">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="66" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H66" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="I66" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="J66" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L66" t="s">
         <v>124</v>
@@ -6485,38 +6492,38 @@
         <v>65</v>
       </c>
       <c r="AJ66" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="67" spans="8:36" x14ac:dyDescent="0.3">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="67" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H67" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="I67" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="J67" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L67" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="M67" t="s">
         <v>83</v>
       </c>
       <c r="AJ67" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="68" spans="8:36" x14ac:dyDescent="0.3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="68" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H68" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="I68" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J68" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L68" t="s">
         <v>122</v>
@@ -6525,18 +6532,18 @@
         <v>83</v>
       </c>
       <c r="AJ68" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="69" spans="8:36" x14ac:dyDescent="0.3">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="69" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H69" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="I69" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="J69" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L69" t="s">
         <v>123</v>
@@ -6545,18 +6552,18 @@
         <v>83</v>
       </c>
       <c r="AJ69" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="70" spans="8:36" x14ac:dyDescent="0.3">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="70" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H70" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="I70" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J70" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L70" t="s">
         <v>149</v>
@@ -6565,18 +6572,18 @@
         <v>83</v>
       </c>
       <c r="AJ70" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="71" spans="8:36" x14ac:dyDescent="0.3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="71" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H71" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="I71" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="J71" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L71" t="s">
         <v>150</v>
@@ -6585,18 +6592,18 @@
         <v>83</v>
       </c>
       <c r="AJ71" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="72" spans="8:36" x14ac:dyDescent="0.3">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="72" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H72" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="I72" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J72" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L72" t="s">
         <v>57</v>
@@ -6605,21 +6612,21 @@
         <v>65</v>
       </c>
       <c r="N72" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="AJ72" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="73" spans="8:36" x14ac:dyDescent="0.3">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="73" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H73" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="I73" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="J73" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L73" t="s">
         <v>136</v>
@@ -6628,15 +6635,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="74" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="74" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H74" t="s">
         <v>174</v>
       </c>
       <c r="I74" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J74" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L74" t="s">
         <v>145</v>
@@ -6645,168 +6652,168 @@
         <v>65</v>
       </c>
     </row>
-    <row r="75" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="75" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H75" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="I75" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J75" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L75" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="M75" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="76" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="76" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H76" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="I76" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J76" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L76" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="M76" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="77" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="77" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H77" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="I77" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="J77" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L77" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="M77" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="78" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="78" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H78" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="I78" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="J78" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L78" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="M78" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="79" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="79" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H79" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="I79" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J79" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L79" t="s">
-        <v>499</v>
+        <v>483</v>
       </c>
       <c r="M79" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="80" spans="8:36" x14ac:dyDescent="0.3">
+    <row r="80" spans="8:36" x14ac:dyDescent="0.35">
       <c r="H80" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="I80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J80" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L80" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="M80" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H81" t="s">
         <v>72</v>
       </c>
       <c r="I81" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J81" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L81" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="M81" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="82" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H82" t="s">
         <v>73</v>
       </c>
       <c r="I82" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J82" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L82" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="M82" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="83" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H83" t="s">
         <v>157</v>
       </c>
       <c r="I83" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J83" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L83" t="s">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="M83" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H84" t="s">
         <v>173</v>
       </c>
       <c r="I84" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J84" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L84" t="s">
         <v>128</v>
@@ -6815,15 +6822,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="85" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H85" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="I85" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J85" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L85" t="s">
         <v>127</v>
@@ -6832,15 +6839,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="86" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H86" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="I86" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="J86" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L86" t="s">
         <v>130</v>
@@ -6849,15 +6856,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="87" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H87" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="I87" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J87" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L87" t="s">
         <v>129</v>
@@ -6866,15 +6873,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="88" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H88" t="s">
         <v>66</v>
       </c>
       <c r="I88" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="J88" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L88" t="s">
         <v>153</v>
@@ -6883,15 +6890,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="89" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H89" t="s">
         <v>67</v>
       </c>
       <c r="I89" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J89" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L89" t="s">
         <v>152</v>
@@ -6900,15 +6907,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="90" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H90" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="I90" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J90" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L90" t="s">
         <v>147</v>
@@ -6917,15 +6924,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="91" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H91" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="I91" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J91" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L91" t="s">
         <v>146</v>
@@ -6934,32 +6941,32 @@
         <v>65</v>
       </c>
     </row>
-    <row r="92" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H92" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="I92" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J92" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L92" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
       <c r="M92" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="93" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H93" t="s">
         <v>69</v>
       </c>
       <c r="I93" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J93" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L93" t="s">
         <v>137</v>
@@ -6968,83 +6975,83 @@
         <v>65</v>
       </c>
     </row>
-    <row r="94" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H94" t="s">
         <v>70</v>
       </c>
       <c r="I94" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J94" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L94" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="M94" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="95" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H95" t="s">
         <v>71</v>
       </c>
       <c r="I95" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J95" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L95" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="M95" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="96" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H96" t="s">
         <v>163</v>
       </c>
       <c r="I96" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J96" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L96" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="M96" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="97" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H97" t="s">
         <v>68</v>
       </c>
       <c r="I97" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J97" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L97" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="M97" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="98" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H98" t="s">
         <v>162</v>
       </c>
       <c r="I98" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J98" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L98" t="s">
         <v>151</v>
@@ -7053,270 +7060,270 @@
         <v>65</v>
       </c>
     </row>
-    <row r="99" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H99" t="s">
         <v>170</v>
       </c>
       <c r="I99" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J99" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L99" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="M99" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="100" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H100" t="s">
         <v>161</v>
       </c>
       <c r="I100" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J100" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L100" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="M100" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="101" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H101" t="s">
         <v>160</v>
       </c>
       <c r="I101" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J101" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L101" t="s">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="M101" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="102" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H102" t="s">
         <v>159</v>
       </c>
       <c r="I102" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J102" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L102" t="s">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="M102" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="103" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H103" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I103" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J103" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L103" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="M103" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="104" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H104" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I104" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J104" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L104" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="M104" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="105" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H105" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="I105" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J105" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L105" t="s">
-        <v>493</v>
+        <v>477</v>
       </c>
       <c r="M105" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="106" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H106" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="I106" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J106" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L106" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="M106" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="107" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H107" t="s">
         <v>74</v>
       </c>
       <c r="I107" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J107" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L107" t="s">
-        <v>495</v>
+        <v>479</v>
       </c>
       <c r="M107" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="108" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H108" t="s">
         <v>75</v>
       </c>
       <c r="I108" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J108" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L108" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="M108" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="109" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H109" t="s">
         <v>156</v>
       </c>
       <c r="I109" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J109" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L109" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="M109" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="110" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H110" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="I110" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J110" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L110" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="M110" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="111" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H111" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="I111" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J111" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L111" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="M111" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="112" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H112" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="I112" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J112" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L112" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="M112" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="113" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H113" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="I113" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="J113" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L113" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="M113" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="114" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="8:13" x14ac:dyDescent="0.35">
       <c r="H114" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="I114" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="J114" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="L114" t="s">
         <v>58</v>
@@ -7325,7 +7332,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="115" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L115" t="s">
         <v>133</v>
       </c>
@@ -7333,7 +7340,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="116" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L116" t="s">
         <v>116</v>
       </c>
@@ -7341,7 +7348,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="117" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L117" t="s">
         <v>144</v>
       </c>
@@ -7349,55 +7356,55 @@
         <v>65</v>
       </c>
     </row>
-    <row r="118" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L118" t="s">
-        <v>491</v>
+        <v>475</v>
       </c>
       <c r="M118" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="119" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L119" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="M119" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="120" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L120" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="M120" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="121" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L121" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="M121" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="122" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L122" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="M122" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="123" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L123" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="M123" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="124" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L124" t="s">
         <v>61</v>
       </c>
@@ -7405,7 +7412,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="125" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L125" t="s">
         <v>62</v>
       </c>
@@ -7413,7 +7420,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="126" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L126" t="s">
         <v>139</v>
       </c>
@@ -7421,7 +7428,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="127" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L127" t="s">
         <v>148</v>
       </c>
@@ -7429,47 +7436,47 @@
         <v>65</v>
       </c>
     </row>
-    <row r="128" spans="8:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="8:13" x14ac:dyDescent="0.35">
       <c r="L128" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="M128" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="129" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L129" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="M129" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="130" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L130" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="M130" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="131" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L131" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="M131" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="132" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L132" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="M132" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="133" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L133" t="s">
         <v>59</v>
       </c>
@@ -7477,47 +7484,47 @@
         <v>65</v>
       </c>
     </row>
-    <row r="134" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L134" t="s">
-        <v>367</v>
+        <v>351</v>
       </c>
       <c r="M134" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="135" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L135" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="M135" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="136" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L136" t="s">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="M136" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="137" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L137" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="M137" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="138" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L138" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="M138" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="139" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L139" t="s">
         <v>125</v>
       </c>
@@ -7525,7 +7532,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="140" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L140" t="s">
         <v>60</v>
       </c>
@@ -7533,7 +7540,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="141" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L141" t="s">
         <v>126</v>
       </c>
@@ -7541,7 +7548,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="142" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L142" t="s">
         <v>138</v>
       </c>
@@ -7549,7 +7556,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="143" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L143" t="s">
         <v>142</v>
       </c>
@@ -7557,23 +7564,23 @@
         <v>83</v>
       </c>
     </row>
-    <row r="144" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L144" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="M144" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="145" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L145" t="s">
-        <v>368</v>
+        <v>352</v>
       </c>
       <c r="M145" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="146" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L146" t="s">
         <v>134</v>
       </c>
@@ -7581,23 +7588,23 @@
         <v>65</v>
       </c>
     </row>
-    <row r="147" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L147" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="M147" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="148" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L148" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="M148" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="149" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L149" t="s">
         <v>140</v>
       </c>
@@ -7605,7 +7612,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="150" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L150" t="s">
         <v>141</v>
       </c>
@@ -7613,23 +7620,23 @@
         <v>65</v>
       </c>
     </row>
-    <row r="151" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L151" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="M151" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="152" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L152" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="M152" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="153" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L153" t="s">
         <v>63</v>
       </c>
@@ -7637,7 +7644,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="154" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L154" t="s">
         <v>64</v>
       </c>
@@ -7645,7 +7652,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="155" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L155" t="s">
         <v>131</v>
       </c>
@@ -7653,23 +7660,23 @@
         <v>65</v>
       </c>
     </row>
-    <row r="156" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L156" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="M156" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="157" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L157" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="M157" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="158" spans="12:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="12:13" x14ac:dyDescent="0.35">
       <c r="L158" t="s">
         <v>56</v>
       </c>
@@ -7713,29 +7720,29 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34ECC9F7-B649-41BF-A742-3CCEA0266A56}">
   <dimension ref="B3:R28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="18.77734375" customWidth="1"/>
-    <col min="6" max="6" width="20.77734375" customWidth="1"/>
+    <col min="5" max="5" width="18.81640625" customWidth="1"/>
+    <col min="6" max="6" width="20.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:15" ht="93.6" x14ac:dyDescent="1.75">
+    <row r="3" spans="2:15" ht="93.5" x14ac:dyDescent="2.1">
       <c r="B3" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
       <c r="J5" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="K5" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="L5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="J6">
         <v>240000000</v>
       </c>
@@ -7746,60 +7753,60 @@
         <v>65534</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="O8">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="O9">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="O10">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="O11">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="O12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="O13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
       <c r="O14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
       <c r="O15">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:18" x14ac:dyDescent="0.35">
       <c r="E20" s="8" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="21" spans="5:18" x14ac:dyDescent="0.3">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="21" spans="5:18" x14ac:dyDescent="0.35">
       <c r="E21" s="6" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="F21" s="6">
         <f>$J$6 *$O$8 / $K$6</f>
@@ -7810,9 +7817,9 @@
         <v>117191.07638782922</v>
       </c>
     </row>
-    <row r="22" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="5:18" x14ac:dyDescent="0.35">
       <c r="E22" s="7" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="F22" s="7">
         <f>$J$6 *$O$9 / $K$6</f>
@@ -7823,9 +7830,9 @@
         <v>58595.53819391461</v>
       </c>
     </row>
-    <row r="23" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="5:18" x14ac:dyDescent="0.35">
       <c r="E23" s="6" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="F23" s="6">
         <f>$J$6 *$O$10 / $K$6</f>
@@ -7839,9 +7846,9 @@
         <v>105</v>
       </c>
     </row>
-    <row r="24" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="5:18" x14ac:dyDescent="0.35">
       <c r="E24" s="7" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="F24" s="7">
         <f>$J$6 *$O$11 / $K$6</f>
@@ -7852,9 +7859,9 @@
         <v>14648.884548478653</v>
       </c>
     </row>
-    <row r="25" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="5:18" x14ac:dyDescent="0.35">
       <c r="E25" s="6" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="F25" s="6">
         <f>$J$6 *$O$12 / $K$6</f>
@@ -7865,9 +7872,9 @@
         <v>7324.4422742393263</v>
       </c>
     </row>
-    <row r="26" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="5:18" x14ac:dyDescent="0.35">
       <c r="E26" s="7" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="F26" s="7">
         <f>$J$6 *$O$13 / $K$6</f>
@@ -7878,9 +7885,9 @@
         <v>3662.2211371196631</v>
       </c>
     </row>
-    <row r="27" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="5:18" x14ac:dyDescent="0.35">
       <c r="E27" s="6" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="F27" s="6">
         <f>$J$6 / $O$14 / $K$6</f>
@@ -7891,9 +7898,9 @@
         <v>1831.1105685598316</v>
       </c>
     </row>
-    <row r="28" spans="5:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="5:18" x14ac:dyDescent="0.35">
       <c r="E28" s="10" t="s">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="F28" s="10">
         <f>$J$6 / $O$15 / $K$6</f>
@@ -7914,48 +7921,50 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{492C7761-01BE-400F-9C40-BE71D85F5C61}">
-  <dimension ref="A2:BB57"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:BB69"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.109375" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" customWidth="1"/>
+    <col min="1" max="1" width="25.08984375" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" customWidth="1"/>
+    <col min="3" max="3" width="25.36328125" customWidth="1"/>
+    <col min="4" max="4" width="35.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="23.77734375" customWidth="1"/>
+    <col min="6" max="6" width="23.81640625" customWidth="1"/>
     <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="22.88671875" customWidth="1"/>
-    <col min="9" max="9" width="15.21875" customWidth="1"/>
-    <col min="10" max="10" width="24.109375" customWidth="1"/>
-    <col min="12" max="12" width="21.109375" customWidth="1"/>
-    <col min="13" max="13" width="17.5546875" customWidth="1"/>
-    <col min="14" max="14" width="18.109375" customWidth="1"/>
-    <col min="15" max="15" width="28.5546875" customWidth="1"/>
-    <col min="16" max="16" width="24.6640625" customWidth="1"/>
-    <col min="18" max="18" width="18.5546875" customWidth="1"/>
-    <col min="19" max="19" width="23.33203125" customWidth="1"/>
-    <col min="20" max="20" width="18.44140625" customWidth="1"/>
-    <col min="21" max="21" width="23.109375" customWidth="1"/>
-    <col min="23" max="23" width="25.109375" customWidth="1"/>
+    <col min="8" max="8" width="22.90625" customWidth="1"/>
+    <col min="9" max="9" width="15.1796875" customWidth="1"/>
+    <col min="10" max="10" width="24.08984375" customWidth="1"/>
+    <col min="12" max="12" width="21.08984375" customWidth="1"/>
+    <col min="13" max="13" width="17.54296875" customWidth="1"/>
+    <col min="14" max="14" width="18.08984375" customWidth="1"/>
+    <col min="15" max="15" width="28.54296875" customWidth="1"/>
+    <col min="16" max="16" width="24.6328125" customWidth="1"/>
+    <col min="17" max="17" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.54296875" customWidth="1"/>
+    <col min="19" max="19" width="23.36328125" customWidth="1"/>
+    <col min="20" max="20" width="18.453125" customWidth="1"/>
+    <col min="21" max="21" width="23.08984375" customWidth="1"/>
+    <col min="23" max="23" width="25.08984375" customWidth="1"/>
     <col min="24" max="24" width="34" customWidth="1"/>
-    <col min="25" max="25" width="16.77734375" customWidth="1"/>
-    <col min="26" max="26" width="20.77734375" customWidth="1"/>
-    <col min="27" max="27" width="16.77734375" customWidth="1"/>
+    <col min="25" max="25" width="16.81640625" customWidth="1"/>
+    <col min="26" max="26" width="20.81640625" customWidth="1"/>
+    <col min="27" max="27" width="16.81640625" customWidth="1"/>
     <col min="30" max="30" width="13" customWidth="1"/>
-    <col min="31" max="31" width="17.6640625" customWidth="1"/>
-    <col min="38" max="38" width="17.21875" customWidth="1"/>
-    <col min="40" max="40" width="19.44140625" customWidth="1"/>
-    <col min="53" max="53" width="40.5546875" customWidth="1"/>
+    <col min="31" max="31" width="17.6328125" customWidth="1"/>
+    <col min="38" max="38" width="17.1796875" customWidth="1"/>
+    <col min="40" max="40" width="19.453125" customWidth="1"/>
+    <col min="53" max="53" width="40.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -7966,13 +7975,7 @@
         <v>51</v>
       </c>
       <c r="L5" t="s">
-        <v>196</v>
-      </c>
-      <c r="P5" t="s">
-        <v>53</v>
-      </c>
-      <c r="R5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="V5" t="s">
         <v>52</v>
@@ -7984,7 +7987,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -8018,24 +8021,6 @@
       <c r="N6" t="s">
         <v>42</v>
       </c>
-      <c r="P6" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>22</v>
-      </c>
-      <c r="R6" t="s">
-        <v>40</v>
-      </c>
-      <c r="S6" t="s">
-        <v>41</v>
-      </c>
-      <c r="T6" t="s">
-        <v>42</v>
-      </c>
-      <c r="U6" t="s">
-        <v>331</v>
-      </c>
       <c r="W6" t="s">
         <v>21</v>
       </c>
@@ -8058,9 +8043,9 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -8072,7 +8057,7 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H7" t="s">
         <v>92</v>
@@ -8084,32 +8069,14 @@
         <v>28</v>
       </c>
       <c r="L7" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="M7" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="N7" t="s">
         <v>43</v>
       </c>
-      <c r="P7" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>29</v>
-      </c>
-      <c r="R7" t="s">
-        <v>340</v>
-      </c>
-      <c r="S7" t="s">
-        <v>5</v>
-      </c>
-      <c r="T7" t="s">
-        <v>43</v>
-      </c>
-      <c r="U7" t="s">
-        <v>334</v>
-      </c>
       <c r="W7" t="s">
         <v>11</v>
       </c>
@@ -8135,9 +8102,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -8149,7 +8116,7 @@
         <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H8" t="s">
         <v>96</v>
@@ -8161,32 +8128,14 @@
         <v>33</v>
       </c>
       <c r="L8" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="M8" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="N8" t="s">
         <v>85</v>
       </c>
-      <c r="P8" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>30</v>
-      </c>
-      <c r="R8" t="s">
-        <v>341</v>
-      </c>
-      <c r="S8" t="s">
-        <v>6</v>
-      </c>
-      <c r="T8" t="s">
-        <v>43</v>
-      </c>
-      <c r="U8" t="s">
-        <v>334</v>
-      </c>
       <c r="W8" t="s">
         <v>12</v>
       </c>
@@ -8197,7 +8146,7 @@
         <v>118</v>
       </c>
       <c r="AA8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AB8" t="s">
         <v>24</v>
@@ -8212,9 +8161,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -8226,7 +8175,7 @@
         <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H9" t="s">
         <v>91</v>
@@ -8238,32 +8187,14 @@
         <v>34</v>
       </c>
       <c r="L9" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="M9" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="N9" t="s">
         <v>48</v>
       </c>
-      <c r="P9" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>31</v>
-      </c>
-      <c r="R9" t="s">
-        <v>555</v>
-      </c>
-      <c r="S9" t="s">
-        <v>535</v>
-      </c>
-      <c r="T9" t="s">
-        <v>43</v>
-      </c>
-      <c r="U9" t="s">
-        <v>334</v>
-      </c>
       <c r="W9" t="s">
         <v>12</v>
       </c>
@@ -8274,7 +8205,7 @@
         <v>119</v>
       </c>
       <c r="AA9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AB9" t="s">
         <v>30</v>
@@ -8289,7 +8220,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -8303,7 +8234,7 @@
         <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H10" t="s">
         <v>93</v>
@@ -8315,7 +8246,7 @@
         <v>36</v>
       </c>
       <c r="L10" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="M10" t="s">
         <v>176</v>
@@ -8323,24 +8254,6 @@
       <c r="N10" t="s">
         <v>43</v>
       </c>
-      <c r="P10" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>32</v>
-      </c>
-      <c r="R10" t="s">
-        <v>556</v>
-      </c>
-      <c r="S10" t="s">
-        <v>534</v>
-      </c>
-      <c r="T10" t="s">
-        <v>43</v>
-      </c>
-      <c r="U10" t="s">
-        <v>334</v>
-      </c>
       <c r="W10" t="s">
         <v>12</v>
       </c>
@@ -8351,7 +8264,7 @@
         <v>120</v>
       </c>
       <c r="AA10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AB10" t="s">
         <v>31</v>
@@ -8366,7 +8279,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="11" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -8380,7 +8293,7 @@
         <v>25</v>
       </c>
       <c r="G11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H11" t="s">
         <v>87</v>
@@ -8392,7 +8305,7 @@
         <v>37</v>
       </c>
       <c r="L11" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="M11" t="s">
         <v>176</v>
@@ -8400,24 +8313,6 @@
       <c r="N11" t="s">
         <v>44</v>
       </c>
-      <c r="P11" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>29</v>
-      </c>
-      <c r="R11" t="s">
-        <v>553</v>
-      </c>
-      <c r="S11" t="s">
-        <v>546</v>
-      </c>
-      <c r="T11" t="s">
-        <v>43</v>
-      </c>
-      <c r="U11" t="s">
-        <v>334</v>
-      </c>
       <c r="W11" t="s">
         <v>12</v>
       </c>
@@ -8440,7 +8335,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="12" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -8454,7 +8349,7 @@
         <v>26</v>
       </c>
       <c r="G12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H12" t="s">
         <v>88</v>
@@ -8466,7 +8361,7 @@
         <v>31</v>
       </c>
       <c r="L12" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="M12" t="s">
         <v>176</v>
@@ -8474,24 +8369,6 @@
       <c r="N12" t="s">
         <v>85</v>
       </c>
-      <c r="P12" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>30</v>
-      </c>
-      <c r="R12" t="s">
-        <v>553</v>
-      </c>
-      <c r="S12" t="s">
-        <v>546</v>
-      </c>
-      <c r="T12" t="s">
-        <v>44</v>
-      </c>
-      <c r="U12" t="s">
-        <v>334</v>
-      </c>
       <c r="W12" t="s">
         <v>12</v>
       </c>
@@ -8514,7 +8391,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -8528,7 +8405,7 @@
         <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H13" t="s">
         <v>97</v>
@@ -8540,7 +8417,7 @@
         <v>32</v>
       </c>
       <c r="L13" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="M13" t="s">
         <v>176</v>
@@ -8548,24 +8425,6 @@
       <c r="N13" t="s">
         <v>48</v>
       </c>
-      <c r="P13" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>23</v>
-      </c>
-      <c r="R13" t="s">
-        <v>552</v>
-      </c>
-      <c r="S13" t="s">
-        <v>178</v>
-      </c>
-      <c r="T13" t="s">
-        <v>43</v>
-      </c>
-      <c r="U13" t="s">
-        <v>334</v>
-      </c>
       <c r="AA13" t="s">
         <v>12</v>
       </c>
@@ -8579,7 +8438,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -8593,7 +8452,7 @@
         <v>24</v>
       </c>
       <c r="G14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H14" t="s">
         <v>98</v>
@@ -8605,34 +8464,16 @@
         <v>24</v>
       </c>
       <c r="L14" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="M14" t="s">
-        <v>545</v>
+        <v>529</v>
       </c>
       <c r="N14" t="s">
         <v>44</v>
       </c>
-      <c r="P14" t="s">
+      <c r="AA14" t="s">
         <v>179</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>32</v>
-      </c>
-      <c r="R14" t="s">
-        <v>557</v>
-      </c>
-      <c r="S14" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" t="s">
-        <v>43</v>
-      </c>
-      <c r="U14" t="s">
-        <v>335</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>180</v>
       </c>
       <c r="AB14" t="s">
         <v>25</v>
@@ -8644,7 +8485,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -8661,28 +8502,10 @@
         <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>342</v>
-      </c>
-      <c r="P15" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="AA15" t="s">
         <v>179</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="R15" t="s">
-        <v>557</v>
-      </c>
-      <c r="S15" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="T15" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="U15" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>180</v>
       </c>
       <c r="AB15" t="s">
         <v>26</v>
@@ -8694,7 +8517,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -8713,26 +8536,8 @@
       <c r="H16" t="s">
         <v>91</v>
       </c>
-      <c r="P16" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="R16" s="6" t="s">
-        <v>554</v>
-      </c>
-      <c r="S16" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="T16" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="U16" s="11" t="s">
-        <v>335</v>
-      </c>
       <c r="AA16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AB16" t="s">
         <v>27</v>
@@ -8744,7 +8549,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -8763,26 +8568,8 @@
       <c r="H17" t="s">
         <v>95</v>
       </c>
-      <c r="P17" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q17" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="R17" t="s">
-        <v>558</v>
-      </c>
-      <c r="S17" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="T17" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="U17" s="13" t="s">
-        <v>332</v>
-      </c>
       <c r="AA17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AB17" t="s">
         <v>28</v>
@@ -8794,7 +8581,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="18" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -8813,24 +8600,6 @@
       <c r="H18" t="s">
         <v>96</v>
       </c>
-      <c r="P18" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="R18" t="s">
-        <v>558</v>
-      </c>
-      <c r="S18" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="T18" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="U18" s="11" t="s">
-        <v>332</v>
-      </c>
       <c r="AA18" t="s">
         <v>11</v>
       </c>
@@ -8844,7 +8613,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -8863,24 +8632,6 @@
       <c r="H19" t="s">
         <v>92</v>
       </c>
-      <c r="P19" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q19" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="R19" t="s">
-        <v>558</v>
-      </c>
-      <c r="S19" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="T19" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="U19" s="13" t="s">
-        <v>332</v>
-      </c>
       <c r="AA19" t="s">
         <v>11</v>
       </c>
@@ -8894,9 +8645,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -8913,24 +8664,6 @@
       <c r="H20" t="s">
         <v>89</v>
       </c>
-      <c r="P20" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="R20" t="s">
-        <v>558</v>
-      </c>
-      <c r="S20" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="T20" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="U20" s="11" t="s">
-        <v>332</v>
-      </c>
       <c r="AA20" t="s">
         <v>12</v>
       </c>
@@ -8944,12 +8677,12 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
         <v>13</v>
@@ -8963,24 +8696,6 @@
       <c r="H21" t="s">
         <v>93</v>
       </c>
-      <c r="P21" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="R21" t="s">
-        <v>558</v>
-      </c>
-      <c r="S21" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="T21" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="U21" s="13" t="s">
-        <v>332</v>
-      </c>
       <c r="AA21" t="s">
         <v>12</v>
       </c>
@@ -8994,33 +8709,15 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
-      </c>
-      <c r="P22" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>31</v>
-      </c>
-      <c r="R22" t="s">
-        <v>558</v>
-      </c>
-      <c r="S22" t="s">
-        <v>336</v>
-      </c>
-      <c r="T22" t="s">
-        <v>44</v>
-      </c>
-      <c r="U22" t="s">
-        <v>332</v>
+        <v>39</v>
       </c>
       <c r="AA22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AB22" t="s">
         <v>33</v>
@@ -9029,33 +8726,15 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>178</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="P23" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>32</v>
-      </c>
-      <c r="R23" t="s">
-        <v>558</v>
-      </c>
-      <c r="S23" t="s">
-        <v>337</v>
-      </c>
-      <c r="T23" t="s">
-        <v>43</v>
-      </c>
-      <c r="U23" t="s">
-        <v>332</v>
+        <v>23</v>
       </c>
       <c r="AA23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AB23" t="s">
         <v>34</v>
@@ -9064,201 +8743,141 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:54" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
-      </c>
-      <c r="P24" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>33</v>
-      </c>
-      <c r="R24" t="s">
-        <v>558</v>
-      </c>
-      <c r="S24" t="s">
-        <v>337</v>
-      </c>
-      <c r="T24" t="s">
-        <v>44</v>
-      </c>
-      <c r="U24" t="s">
-        <v>332</v>
+        <v>24</v>
       </c>
       <c r="AA24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AB24" t="s">
         <v>36</v>
       </c>
       <c r="BB24" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="25" spans="1:54" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="25" spans="1:54" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA25" t="s">
         <v>179</v>
-      </c>
-      <c r="B25" t="s">
-        <v>23</v>
-      </c>
-      <c r="P25" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>34</v>
-      </c>
-      <c r="R25" t="s">
-        <v>558</v>
-      </c>
-      <c r="S25" t="s">
-        <v>338</v>
-      </c>
-      <c r="T25" t="s">
-        <v>43</v>
-      </c>
-      <c r="U25" t="s">
-        <v>332</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>180</v>
       </c>
       <c r="AB25" t="s">
         <v>37</v>
       </c>
       <c r="BB25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="26" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>179</v>
-      </c>
-      <c r="B26" t="s">
-        <v>24</v>
-      </c>
+        <v>456</v>
+      </c>
+    </row>
+    <row r="26" spans="1:54" x14ac:dyDescent="0.35">
       <c r="AA26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AB26" t="s">
         <v>33</v>
       </c>
       <c r="BB26" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="27" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" t="s">
-        <v>28</v>
-      </c>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="27" spans="1:54" x14ac:dyDescent="0.35">
       <c r="W27" t="s">
+        <v>250</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:54" x14ac:dyDescent="0.35">
+      <c r="W28" t="s">
+        <v>249</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>178</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:54" x14ac:dyDescent="0.35">
+      <c r="W29" t="s">
         <v>251</v>
-      </c>
-      <c r="AA27" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="W28" t="s">
-        <v>250</v>
-      </c>
-      <c r="AA28" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB28" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="W29" t="s">
-        <v>252</v>
       </c>
       <c r="AA29" t="s">
         <v>179</v>
       </c>
       <c r="AB29" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="1:54" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:54" x14ac:dyDescent="0.35">
       <c r="W30" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="31" spans="1:54" x14ac:dyDescent="0.35">
+      <c r="W31" t="s">
         <v>253</v>
       </c>
-      <c r="AA30" t="s">
-        <v>179</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="31" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="W31" t="s">
+    </row>
+    <row r="32" spans="1:54" x14ac:dyDescent="0.35">
+      <c r="W32" t="s">
         <v>254</v>
       </c>
-      <c r="AA31" t="s">
-        <v>180</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="W32" t="s">
+    </row>
+    <row r="33" spans="11:23" x14ac:dyDescent="0.35">
+      <c r="W33" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="33" spans="11:23" x14ac:dyDescent="0.3">
-      <c r="W33" t="s">
+    <row r="34" spans="11:23" x14ac:dyDescent="0.35">
+      <c r="W34" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="34" spans="11:23" x14ac:dyDescent="0.3">
-      <c r="W34" t="s">
+    <row r="35" spans="11:23" x14ac:dyDescent="0.35">
+      <c r="K35" t="s">
+        <v>520</v>
+      </c>
+      <c r="W35" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="35" spans="11:23" x14ac:dyDescent="0.3">
-      <c r="K35" t="s">
-        <v>536</v>
-      </c>
-      <c r="W35" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="36" spans="11:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="11:23" x14ac:dyDescent="0.35">
       <c r="K36" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="L36" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
       <c r="M36" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="N36" t="s">
-        <v>542</v>
+        <v>526</v>
       </c>
       <c r="O36" t="s">
-        <v>537</v>
+        <v>521</v>
       </c>
       <c r="P36" t="s">
-        <v>538</v>
+        <v>522</v>
       </c>
       <c r="Q36" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="37" spans="11:23" x14ac:dyDescent="0.3">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="37" spans="11:23" x14ac:dyDescent="0.35">
       <c r="K37" t="s">
         <v>10</v>
       </c>
@@ -9272,24 +8891,24 @@
         <v>39</v>
       </c>
       <c r="O37" t="s">
-        <v>547</v>
+        <v>531</v>
       </c>
       <c r="P37" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="Q37" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="38" spans="11:23" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="38" spans="11:23" x14ac:dyDescent="0.35">
       <c r="K38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L38" t="s">
         <v>28</v>
       </c>
       <c r="M38" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="N38" t="s">
         <v>29</v>
@@ -9298,38 +8917,61 @@
         <v>4</v>
       </c>
       <c r="P38" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="Q38" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="44" spans="11:23" x14ac:dyDescent="0.3">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="39" spans="11:23" x14ac:dyDescent="0.35">
+      <c r="K39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L39" t="s">
+        <v>29</v>
+      </c>
+      <c r="M39" t="s">
+        <v>9</v>
+      </c>
+      <c r="N39" t="s">
+        <v>30</v>
+      </c>
+      <c r="O39" t="s">
+        <v>530</v>
+      </c>
+      <c r="P39" t="s">
+        <v>528</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="44" spans="11:23" x14ac:dyDescent="0.35">
       <c r="K44" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="45" spans="11:23" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="45" spans="11:23" x14ac:dyDescent="0.35">
       <c r="K45" t="s">
+        <v>197</v>
+      </c>
+      <c r="L45" t="s">
         <v>198</v>
       </c>
-      <c r="L45" t="s">
+      <c r="M45" t="s">
         <v>199</v>
       </c>
-      <c r="M45" t="s">
+      <c r="N45" t="s">
         <v>200</v>
-      </c>
-      <c r="N45" t="s">
-        <v>201</v>
       </c>
       <c r="O45" t="s">
         <v>40</v>
       </c>
       <c r="P45" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="46" spans="11:23" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="46" spans="11:23" x14ac:dyDescent="0.35">
       <c r="K46" t="s">
         <v>12</v>
       </c>
@@ -9343,13 +8985,13 @@
         <v>36</v>
       </c>
       <c r="O46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P46" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="47" spans="11:23" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="47" spans="11:23" x14ac:dyDescent="0.35">
       <c r="K47" s="12" t="s">
         <v>10</v>
       </c>
@@ -9363,30 +9005,396 @@
         <v>37</v>
       </c>
       <c r="O47" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="P47" s="11" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="57" spans="36:36" x14ac:dyDescent="0.3">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="51" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C51" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="52" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C52" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" t="s">
+        <v>40</v>
+      </c>
+      <c r="F52" t="s">
+        <v>41</v>
+      </c>
+      <c r="G52" t="s">
+        <v>42</v>
+      </c>
+      <c r="H52" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="53" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>29</v>
+      </c>
+      <c r="E53" t="s">
+        <v>324</v>
+      </c>
+      <c r="F53" t="s">
+        <v>5</v>
+      </c>
+      <c r="G53" t="s">
+        <v>43</v>
+      </c>
+      <c r="H53" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="54" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" t="s">
+        <v>325</v>
+      </c>
+      <c r="F54" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" t="s">
+        <v>43</v>
+      </c>
+      <c r="H54" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" t="s">
+        <v>538</v>
+      </c>
+      <c r="F55" t="s">
+        <v>519</v>
+      </c>
+      <c r="G55" t="s">
+        <v>43</v>
+      </c>
+      <c r="H55" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="56" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>32</v>
+      </c>
+      <c r="E56" t="s">
+        <v>539</v>
+      </c>
+      <c r="F56" t="s">
+        <v>518</v>
+      </c>
+      <c r="G56" t="s">
+        <v>43</v>
+      </c>
+      <c r="H56" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="57" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C57" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" t="s">
+        <v>536</v>
+      </c>
+      <c r="F57" t="s">
+        <v>177</v>
+      </c>
+      <c r="G57" t="s">
+        <v>43</v>
+      </c>
+      <c r="H57" t="s">
+        <v>318</v>
+      </c>
       <c r="AJ57" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C58" t="s">
+        <v>178</v>
+      </c>
+      <c r="D58" t="s">
+        <v>32</v>
+      </c>
+      <c r="E58" t="s">
+        <v>540</v>
+      </c>
+      <c r="F58" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" t="s">
+        <v>43</v>
+      </c>
+      <c r="H58" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="59" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C59" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E59" t="s">
+        <v>540</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="60" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C60" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" t="s">
+        <v>540</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H60" s="11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="61" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C61" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E61" t="s">
+        <v>540</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="62" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C62" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" t="s">
+        <v>541</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H62" s="13" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="63" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C63" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E63" t="s">
+        <v>541</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="64" spans="3:36" x14ac:dyDescent="0.35">
+      <c r="C64" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" t="s">
+        <v>541</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H64" s="13" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="65" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="C65" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E65" t="s">
+        <v>541</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="66" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="C66" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" t="s">
+        <v>31</v>
+      </c>
+      <c r="E66" t="s">
+        <v>541</v>
+      </c>
+      <c r="F66" t="s">
+        <v>320</v>
+      </c>
+      <c r="G66" t="s">
+        <v>44</v>
+      </c>
+      <c r="H66" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="67" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" t="s">
+        <v>32</v>
+      </c>
+      <c r="E67" t="s">
+        <v>541</v>
+      </c>
+      <c r="F67" t="s">
+        <v>321</v>
+      </c>
+      <c r="G67" t="s">
+        <v>43</v>
+      </c>
+      <c r="H67" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="68" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="C68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" t="s">
+        <v>33</v>
+      </c>
+      <c r="E68" t="s">
+        <v>541</v>
+      </c>
+      <c r="F68" t="s">
+        <v>321</v>
+      </c>
+      <c r="G68" t="s">
+        <v>44</v>
+      </c>
+      <c r="H68" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="69" spans="3:8" x14ac:dyDescent="0.35">
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" t="s">
+        <v>34</v>
+      </c>
+      <c r="E69" t="s">
+        <v>541</v>
+      </c>
+      <c r="F69" t="s">
+        <v>322</v>
+      </c>
+      <c r="G69" t="s">
+        <v>43</v>
+      </c>
+      <c r="H69" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX22 Q7 K7:K14 X7:X12 B7:B27 AB8:AB31 Q15:Q21 F7:F21" xr:uid="{14BC2D73-1395-4E2C-9D1E-55C781825C64}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX22 D53 K7:K14 X7:X12 F7:F21 B7:B25 AB8:AB29 D59:D65" xr:uid="{14BC2D73-1395-4E2C-9D1E-55C781825C64}">
       <formula1>$AX$6:$AX$21</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U26:U27" xr:uid="{843CAB93-5FB8-4584-AA77-D87D9BF50E6D}">
       <formula1>"HrTim,Tim"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U7 U12:U21" xr:uid="{2E700A6E-F322-4D4F-87DE-D704594A5EA0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H53 H57:H65" xr:uid="{2E700A6E-F322-4D4F-87DE-D704594A5EA0}">
       <formula1>"HrTim,BscTim,AdvTim"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T7 N7:N14 T15:T21" xr:uid="{727A5344-B28A-4866-9EC1-7C96029AF8B6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G53 N7:N14 G59:G65" xr:uid="{727A5344-B28A-4866-9EC1-7C96029AF8B6}">
       <formula1>$AZ$7:$AZ$10</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7:H21" xr:uid="{FFFA1AF2-B35F-4BAA-AEF6-4A6121806F8D}">
@@ -9428,7 +9436,7 @@
           <x14:formula1>
             <xm:f>General_Info!$T$44:$T$51</xm:f>
           </x14:formula1>
-          <xm:sqref>AA8:AA31 P7:P25</xm:sqref>
+          <xm:sqref>AA8:AA29 C53:C69</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3C428027-B16D-4B04-9CB2-8290577ED0FB}">
           <x14:formula1>
@@ -9445,12 +9453,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E52BA6-3E0A-4F7C-9391-164B38476F25}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="22.21875" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="26.6640625" customWidth="1"/>
+    <col min="2" max="2" width="19.453125" customWidth="1"/>
+    <col min="3" max="3" width="22.1796875" customWidth="1"/>
+    <col min="6" max="6" width="31.36328125" customWidth="1"/>
+    <col min="7" max="7" width="26.6328125" customWidth="1"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -9461,44 +9469,44 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BF150CB-3330-4180-96AC-4A3D28CDB7F6}">
   <dimension ref="Y5:Y11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="25" max="25" width="27.21875" customWidth="1"/>
+    <col min="25" max="25" width="27.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="25:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="25:25" x14ac:dyDescent="0.35">
       <c r="Y5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="25:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="25:25" x14ac:dyDescent="0.35">
       <c r="Y6" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="7" spans="25:25" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="7" spans="25:25" x14ac:dyDescent="0.35">
       <c r="Y7" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="8" spans="25:25" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="25:25" x14ac:dyDescent="0.35">
       <c r="Y8" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="9" spans="25:25" x14ac:dyDescent="0.3">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9" spans="25:25" x14ac:dyDescent="0.35">
       <c r="Y9" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="10" spans="25:25" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="10" spans="25:25" x14ac:dyDescent="0.35">
       <c r="Y10" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="11" spans="25:25" x14ac:dyDescent="0.3">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="11" spans="25:25" x14ac:dyDescent="0.35">
       <c r="Y11" t="s">
-        <v>327</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -9512,34 +9520,34 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0962FBCC-E1F3-44E3-92A8-D1FF17927B08}">
   <dimension ref="E2:W20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="23.44140625" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" customWidth="1"/>
-    <col min="9" max="9" width="43.88671875" customWidth="1"/>
-    <col min="10" max="10" width="21.6640625" customWidth="1"/>
-    <col min="11" max="11" width="11.5546875" customWidth="1"/>
-    <col min="12" max="12" width="24.109375" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" customWidth="1"/>
+    <col min="6" max="6" width="22.453125" customWidth="1"/>
+    <col min="9" max="9" width="43.90625" customWidth="1"/>
+    <col min="10" max="10" width="21.6328125" customWidth="1"/>
+    <col min="11" max="11" width="11.54296875" customWidth="1"/>
+    <col min="12" max="12" width="24.08984375" customWidth="1"/>
     <col min="17" max="17" width="45" customWidth="1"/>
-    <col min="18" max="18" width="28.88671875" customWidth="1"/>
-    <col min="19" max="19" width="21.88671875" customWidth="1"/>
-    <col min="20" max="20" width="19.21875" customWidth="1"/>
-    <col min="22" max="22" width="18.5546875" customWidth="1"/>
+    <col min="18" max="18" width="28.90625" customWidth="1"/>
+    <col min="19" max="19" width="21.90625" customWidth="1"/>
+    <col min="20" max="20" width="19.1796875" customWidth="1"/>
+    <col min="22" max="22" width="18.54296875" customWidth="1"/>
     <col min="23" max="23" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:17" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="5:17" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="I2" s="3" t="s">
         <v>110</v>
       </c>
       <c r="J2" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="5:17" x14ac:dyDescent="0.35">
       <c r="I3" t="s">
         <v>107</v>
       </c>
@@ -9553,90 +9561,90 @@
         <v>112</v>
       </c>
       <c r="M3" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="4" spans="5:17" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="5:17" x14ac:dyDescent="0.35">
       <c r="I4" t="s">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="J4" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="K4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M4" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="5" spans="5:17" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5" spans="5:17" x14ac:dyDescent="0.35">
       <c r="I5" t="s">
         <v>106</v>
       </c>
       <c r="J5" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="K5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L5" t="s">
-        <v>104</v>
+        <v>326</v>
       </c>
       <c r="M5" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="6" spans="5:17" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="5:17" x14ac:dyDescent="0.35">
       <c r="I6" t="s">
-        <v>521</v>
+        <v>505</v>
       </c>
       <c r="J6" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="K6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L6" t="s">
-        <v>104</v>
+        <v>326</v>
       </c>
       <c r="M6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="7" spans="5:17" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="7" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="8" spans="5:17" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="9" spans="5:17" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="9" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E9" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="F9" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="10" spans="5:17" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F10" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="17" spans="20:23" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="17" spans="20:23" x14ac:dyDescent="0.35">
       <c r="T17" t="s">
         <v>109</v>
       </c>
@@ -9650,46 +9658,46 @@
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="20:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="20:23" x14ac:dyDescent="0.35">
       <c r="T18" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="U18" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="V18" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W18" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="19" spans="20:23" x14ac:dyDescent="0.3">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="19" spans="20:23" x14ac:dyDescent="0.35">
       <c r="T19" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="U19" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="V19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W19" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="20" spans="20:23" x14ac:dyDescent="0.3">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="20" spans="20:23" x14ac:dyDescent="0.35">
       <c r="T20" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="U20" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="V20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="W20" t="s">
-        <v>342</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -9723,45 +9731,45 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06E18236-E25D-41B3-8B1E-0194276152B3}">
-  <dimension ref="B1:P25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B1:P27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" customWidth="1"/>
-    <col min="10" max="10" width="36.6640625" customWidth="1"/>
-    <col min="11" max="11" width="21.77734375" customWidth="1"/>
-    <col min="16" max="16" width="25.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.36328125" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="10" max="10" width="36.6328125" customWidth="1"/>
+    <col min="11" max="11" width="21.81640625" customWidth="1"/>
+    <col min="16" max="16" width="25.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" t="s">
         <v>241</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>242</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>243</v>
       </c>
-      <c r="E2" t="s">
-        <v>244</v>
-      </c>
       <c r="J2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" t="s">
         <v>238</v>
-      </c>
-      <c r="C3" t="s">
-        <v>239</v>
       </c>
       <c r="D3" t="s">
         <v>43</v>
@@ -9770,21 +9778,21 @@
         <v>65</v>
       </c>
       <c r="J3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="K3" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="P3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="C4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D4" t="s">
         <v>44</v>
@@ -9793,24 +9801,24 @@
         <v>65</v>
       </c>
       <c r="J4" t="s">
-        <v>265</v>
+        <v>566</v>
       </c>
       <c r="K4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L4" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="P4" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="C5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D5" t="s">
         <v>85</v>
@@ -9819,21 +9827,21 @@
         <v>65</v>
       </c>
       <c r="J5" t="s">
+        <v>550</v>
+      </c>
+      <c r="K5" t="s">
         <v>266</v>
       </c>
-      <c r="K5" t="s">
-        <v>282</v>
-      </c>
       <c r="P5" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="6" spans="2:16" x14ac:dyDescent="0.3">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="C6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D6" t="s">
         <v>48</v>
@@ -9842,98 +9850,98 @@
         <v>65</v>
       </c>
       <c r="J6" t="s">
-        <v>267</v>
+        <v>551</v>
       </c>
       <c r="K6" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E7" t="s">
         <v>65</v>
       </c>
       <c r="J7" t="s">
-        <v>268</v>
+        <v>552</v>
       </c>
       <c r="K7" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E8" t="s">
         <v>65</v>
       </c>
       <c r="J8" t="s">
-        <v>269</v>
+        <v>553</v>
       </c>
       <c r="K8" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="C9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E9" t="s">
         <v>65</v>
       </c>
       <c r="J9" t="s">
-        <v>270</v>
+        <v>554</v>
       </c>
       <c r="K9" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="C10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D10" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="E10" t="s">
         <v>65</v>
       </c>
       <c r="J10" t="s">
-        <v>271</v>
+        <v>555</v>
       </c>
       <c r="K10" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D11" t="s">
         <v>43</v>
@@ -9942,69 +9950,112 @@
         <v>65</v>
       </c>
       <c r="J11" t="s">
+        <v>556</v>
+      </c>
+      <c r="K11" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B12" t="s">
+        <v>569</v>
+      </c>
+      <c r="C12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D12" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>570</v>
+      </c>
+      <c r="C13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" s="12" t="s">
         <v>567</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K13" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="J14" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="K14" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="J15" s="14" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="J16" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="K16" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="17" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="14" t="s">
+        <v>561</v>
+      </c>
+      <c r="K17" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="18" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="12" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="19" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J19" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="20" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J20" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="21" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J21" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="J12" s="15" t="s">
-        <v>260</v>
-      </c>
-      <c r="K12" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="J13" s="16" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="J14" s="15" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="J15" s="16" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="J16" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="17" spans="10:10" x14ac:dyDescent="0.3">
-      <c r="J17" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.3">
-      <c r="J18" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="19" spans="10:10" x14ac:dyDescent="0.3">
-      <c r="J19" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="21" spans="10:10" x14ac:dyDescent="0.3">
-      <c r="J21" s="15"/>
-    </row>
-    <row r="22" spans="10:10" x14ac:dyDescent="0.3">
-      <c r="J22" s="16"/>
-    </row>
-    <row r="23" spans="10:10" x14ac:dyDescent="0.3">
-      <c r="J23" s="15"/>
-    </row>
-    <row r="24" spans="10:10" x14ac:dyDescent="0.3">
-      <c r="J24" s="16"/>
-    </row>
-    <row r="25" spans="10:10" x14ac:dyDescent="0.3">
-      <c r="J25" s="15"/>
+    <row r="23" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J23" s="12"/>
+    </row>
+    <row r="24" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="10:11" x14ac:dyDescent="0.35">
+      <c r="J27" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10019,45 +10070,45 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9D1D4C8-FD0D-4DBE-B311-5297C41CC83F}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D5" t="s">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="E5" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="F5" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="G5" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="D6" t="s">
-        <v>347</v>
+        <v>331</v>
       </c>
       <c r="E6" t="s">
         <v>172</v>
@@ -10069,12 +10120,12 @@
         <v>120</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="D7" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="E7" t="s">
         <v>172</v>
@@ -10086,14 +10137,14 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -10109,55 +10160,55 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E85D06B3-E762-495B-BF06-A6CD7E704A4C}">
   <dimension ref="E2:M10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.6328125" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
-    <col min="9" max="9" width="18.44140625" customWidth="1"/>
-    <col min="10" max="10" width="20.44140625" customWidth="1"/>
-    <col min="11" max="11" width="23.33203125" customWidth="1"/>
-    <col min="12" max="12" width="18.6640625" customWidth="1"/>
-    <col min="13" max="13" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="19.6328125" customWidth="1"/>
+    <col min="7" max="7" width="15.36328125" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
+    <col min="9" max="9" width="18.453125" customWidth="1"/>
+    <col min="10" max="10" width="20.453125" customWidth="1"/>
+    <col min="11" max="11" width="23.36328125" customWidth="1"/>
+    <col min="12" max="12" width="18.6328125" customWidth="1"/>
+    <col min="13" max="13" width="19.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E2" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="F2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="G2" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="H2" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="I2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J2" t="s">
         <v>198</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>199</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>200</v>
-      </c>
-      <c r="L2" t="s">
-        <v>201</v>
       </c>
       <c r="M2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E3" t="s">
         <v>74</v>
       </c>
       <c r="F3" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="G3">
         <v>1024</v>
@@ -10178,15 +10229,15 @@
         <v>29</v>
       </c>
       <c r="M3" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="4" spans="5:13" x14ac:dyDescent="0.3">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="4" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E4" t="s">
         <v>75</v>
       </c>
       <c r="F4" t="s">
-        <v>295</v>
+        <v>279</v>
       </c>
       <c r="G4">
         <v>1024</v>
@@ -10207,43 +10258,58 @@
         <v>25</v>
       </c>
       <c r="M4" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="5" spans="5:13" x14ac:dyDescent="0.3">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="5" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E5" t="s">
         <v>156</v>
       </c>
       <c r="F5" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="5:13" x14ac:dyDescent="0.3">
+        <v>1024</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="6" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" t="s">
+        <v>281</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="5:13" x14ac:dyDescent="0.35">
+      <c r="E7" t="s">
         <v>191</v>
       </c>
-      <c r="F6" t="s">
-        <v>297</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="5:13" x14ac:dyDescent="0.3">
-      <c r="E7" t="s">
-        <v>192</v>
-      </c>
       <c r="F7" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -10252,12 +10318,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E8" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="F8" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="G8">
         <v>1024</v>
@@ -10266,27 +10332,27 @@
         <v>1024</v>
       </c>
       <c r="I8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J8" t="s">
         <v>32</v>
       </c>
       <c r="K8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L8" t="s">
         <v>38</v>
       </c>
       <c r="M8" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="9" spans="5:13" x14ac:dyDescent="0.3">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="9" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E9" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="F9" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -10295,12 +10361,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="5:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E10" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="F10" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -10321,35 +10387,35 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{860CCB6B-9BC8-4B28-B4AE-B22F38F81573}">
   <dimension ref="B1:P254"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="17.5546875" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" customWidth="1"/>
-    <col min="10" max="10" width="38.21875" customWidth="1"/>
-    <col min="11" max="11" width="20.5546875" customWidth="1"/>
-    <col min="13" max="13" width="20.5546875" customWidth="1"/>
-    <col min="15" max="15" width="20.21875" customWidth="1"/>
+    <col min="4" max="4" width="17.54296875" customWidth="1"/>
+    <col min="5" max="5" width="17.08984375" customWidth="1"/>
+    <col min="10" max="10" width="38.1796875" customWidth="1"/>
+    <col min="11" max="11" width="20.54296875" customWidth="1"/>
+    <col min="13" max="13" width="20.54296875" customWidth="1"/>
+    <col min="15" max="15" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:14" ht="93.6" x14ac:dyDescent="1.75">
+    <row r="1" spans="3:14" ht="93.5" x14ac:dyDescent="2.1">
       <c r="D1" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C3">
         <v>1000000</v>
       </c>
     </row>
-    <row r="4" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:14" x14ac:dyDescent="0.35">
       <c r="L4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5" spans="3:14" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" spans="3:14" x14ac:dyDescent="0.35">
       <c r="L5">
         <v>65000</v>
       </c>
@@ -10357,24 +10423,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:14" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E7" t="s">
+        <v>215</v>
+      </c>
+      <c r="F7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" t="s">
+        <v>214</v>
+      </c>
+      <c r="J7" t="s">
         <v>217</v>
       </c>
-      <c r="E7" t="s">
-        <v>216</v>
-      </c>
-      <c r="F7" t="s">
-        <v>214</v>
-      </c>
-      <c r="G7" t="s">
-        <v>215</v>
-      </c>
-      <c r="J7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.35">
       <c r="D8">
         <v>8000</v>
       </c>
@@ -10392,46 +10458,46 @@
         <v>1969.2307692307693</v>
       </c>
       <c r="M8" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="9" spans="3:14" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="3:14" x14ac:dyDescent="0.35">
       <c r="M9">
         <f>J14-ROUND(J14,0)</f>
         <v>0.24615384615384617</v>
       </c>
     </row>
-    <row r="12" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:14" x14ac:dyDescent="0.35">
       <c r="D12">
         <f>(E8*C3)/((F8+1)*(G8+1))</f>
         <v>39.99972500189061</v>
       </c>
       <c r="L12" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="13" spans="3:14" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="3:14" x14ac:dyDescent="0.35">
       <c r="J13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L13" t="e">
         <f>L5+(L5/J15)*M9</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:14" x14ac:dyDescent="0.35">
       <c r="J14">
         <f>E8*C3/(D8*(L5))</f>
         <v>0.24615384615384617</v>
       </c>
     </row>
-    <row r="15" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:14" x14ac:dyDescent="0.35">
       <c r="J15">
         <f>TRUNC(J14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:14" x14ac:dyDescent="0.35">
       <c r="D16">
         <f>E8*C3/D8</f>
         <v>16000</v>
@@ -10440,15 +10506,15 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
       <c r="J17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L17" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D18">
         <f>E8*C3/D16</f>
         <v>8000</v>
@@ -10462,7 +10528,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -10478,15 +10544,15 @@
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D28" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K28" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D29">
         <v>1000000</v>
       </c>
@@ -10495,46 +10561,46 @@
         <v>0.5</v>
       </c>
       <c r="M29" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="D30" t="s">
+        <v>226</v>
+      </c>
+      <c r="E30" t="s">
+        <v>227</v>
+      </c>
+      <c r="F30" t="s">
+        <v>229</v>
+      </c>
+      <c r="G30" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="D30" t="s">
-        <v>227</v>
-      </c>
-      <c r="E30" t="s">
-        <v>228</v>
-      </c>
-      <c r="F30" t="s">
-        <v>230</v>
-      </c>
-      <c r="G30" t="s">
-        <v>215</v>
-      </c>
       <c r="I30" t="s">
+        <v>233</v>
+      </c>
+      <c r="J30" t="s">
+        <v>231</v>
+      </c>
+      <c r="K30" t="s">
         <v>234</v>
       </c>
-      <c r="J30" t="s">
+      <c r="L30" t="s">
+        <v>235</v>
+      </c>
+      <c r="M30" t="s">
         <v>232</v>
       </c>
-      <c r="K30" t="s">
-        <v>235</v>
-      </c>
-      <c r="L30" t="s">
+      <c r="O30" t="s">
         <v>236</v>
-      </c>
-      <c r="M30" t="s">
-        <v>233</v>
-      </c>
-      <c r="O30" t="s">
-        <v>237</v>
       </c>
       <c r="P30" t="e">
         <f>2^#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
       <c r="D31">
         <v>2000</v>
       </c>
@@ -10572,7 +10638,7 @@
         <v>0.59998942068653971</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.35">
       <c r="I32">
         <v>20</v>
       </c>
@@ -10597,7 +10663,7 @@
         <v>19.999645006301137</v>
       </c>
     </row>
-    <row r="33" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I33">
         <f>50+I32</f>
         <v>70</v>
@@ -10623,7 +10689,7 @@
         <v>69.998744397522373</v>
       </c>
     </row>
-    <row r="34" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I34">
         <f t="shared" ref="I34:I97" si="5">50+I33</f>
         <v>120</v>
@@ -10649,7 +10715,7 @@
         <v>119.9978400388793</v>
       </c>
     </row>
-    <row r="35" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I35">
         <f t="shared" si="5"/>
         <v>170</v>
@@ -10679,7 +10745,7 @@
         <v>169.99692943046216</v>
       </c>
     </row>
-    <row r="36" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I36">
         <f t="shared" si="5"/>
         <v>220</v>
@@ -10709,7 +10775,7 @@
         <v>219.99606757029218</v>
       </c>
     </row>
-    <row r="37" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I37">
         <f t="shared" si="5"/>
         <v>270</v>
@@ -10739,7 +10805,7 @@
         <v>269.99498821803121</v>
       </c>
     </row>
-    <row r="38" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I38">
         <f t="shared" si="5"/>
         <v>320</v>
@@ -10769,7 +10835,7 @@
         <v>319.99424010367812</v>
       </c>
     </row>
-    <row r="39" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I39">
         <f t="shared" si="5"/>
         <v>370</v>
@@ -10799,7 +10865,7 @@
         <v>369.99315512663014</v>
       </c>
     </row>
-    <row r="40" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I40">
         <f t="shared" si="5"/>
         <v>420</v>
@@ -10829,7 +10895,7 @@
         <v>419.99228264180647</v>
       </c>
     </row>
-    <row r="41" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I41">
         <f t="shared" si="5"/>
         <v>470</v>
@@ -10859,7 +10925,7 @@
         <v>469.99033582371959</v>
       </c>
     </row>
-    <row r="42" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I42">
         <f t="shared" si="5"/>
         <v>520</v>
@@ -10889,7 +10955,7 @@
         <v>519.9898601977261</v>
       </c>
     </row>
-    <row r="43" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I43">
         <f t="shared" si="5"/>
         <v>570</v>
@@ -10919,7 +10985,7 @@
         <v>569.98984705584928</v>
       </c>
     </row>
-    <row r="44" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I44">
         <f t="shared" si="5"/>
         <v>620</v>
@@ -10949,7 +11015,7 @@
         <v>619.98798773273768</v>
       </c>
     </row>
-    <row r="45" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I45">
         <f t="shared" si="5"/>
         <v>670</v>
@@ -10979,7 +11045,7 @@
         <v>669.98597216870769</v>
       </c>
     </row>
-    <row r="46" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I46">
         <f t="shared" si="5"/>
         <v>720</v>
@@ -11009,7 +11075,7 @@
         <v>719.98704023327582</v>
       </c>
     </row>
-    <row r="47" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I47">
         <f t="shared" si="5"/>
         <v>770</v>
@@ -11039,7 +11105,7 @@
         <v>769.98517778532755</v>
       </c>
     </row>
-    <row r="48" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I48">
         <f t="shared" si="5"/>
         <v>820</v>
@@ -11069,7 +11135,7 @@
         <v>819.98319034459792</v>
       </c>
     </row>
-    <row r="49" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I49">
         <f t="shared" si="5"/>
         <v>870</v>
@@ -11099,7 +11165,7 @@
         <v>869.98107791155542</v>
       </c>
     </row>
-    <row r="50" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I50">
         <f t="shared" si="5"/>
         <v>920</v>
@@ -11129,7 +11195,7 @@
         <v>919.97884048666879</v>
       </c>
     </row>
-    <row r="51" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I51">
         <f t="shared" si="5"/>
         <v>970</v>
@@ -11159,7 +11225,7 @@
         <v>969.98235844585577</v>
       </c>
     </row>
-    <row r="52" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I52">
         <f t="shared" si="5"/>
         <v>1020</v>
@@ -11189,7 +11255,7 @@
         <v>1019.9804928730738</v>
       </c>
     </row>
-    <row r="53" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I53">
         <f t="shared" si="5"/>
         <v>1070</v>
@@ -11219,7 +11285,7 @@
         <v>1069.9785335556708</v>
       </c>
     </row>
-    <row r="54" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I54">
         <f t="shared" si="5"/>
         <v>1120</v>
@@ -11249,7 +11315,7 @@
         <v>1119.9764804939098</v>
       </c>
     </row>
-    <row r="55" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I55">
         <f t="shared" si="5"/>
         <v>1170</v>
@@ -11279,7 +11345,7 @@
         <v>1169.9743336880547</v>
       </c>
     </row>
-    <row r="56" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I56">
         <f t="shared" si="5"/>
         <v>1220</v>
@@ -11309,7 +11375,7 @@
         <v>1219.9720931383697</v>
       </c>
     </row>
-    <row r="57" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I57">
         <f t="shared" si="5"/>
         <v>1270</v>
@@ -11339,7 +11405,7 @@
         <v>1269.9697588451177</v>
       </c>
     </row>
-    <row r="58" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I58">
         <f t="shared" si="5"/>
         <v>1320</v>
@@ -11369,7 +11435,7 @@
         <v>1319.9673308085623</v>
       </c>
     </row>
-    <row r="59" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I59">
         <f t="shared" si="5"/>
         <v>1370</v>
@@ -11399,7 +11465,7 @@
         <v>1369.9648090289681</v>
       </c>
     </row>
-    <row r="60" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I60">
         <f t="shared" si="5"/>
         <v>1420</v>
@@ -11429,7 +11495,7 @@
         <v>1419.9747954473808</v>
       </c>
     </row>
-    <row r="61" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I61">
         <f t="shared" si="5"/>
         <v>1470</v>
@@ -11459,7 +11525,7 @@
         <v>1469.9729892463226</v>
       </c>
     </row>
-    <row r="62" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I62">
         <f t="shared" si="5"/>
         <v>1520</v>
@@ -11489,7 +11555,7 @@
         <v>1519.9711205487097</v>
       </c>
     </row>
-    <row r="63" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I63">
         <f t="shared" si="5"/>
         <v>1570</v>
@@ -11519,7 +11585,7 @@
         <v>1569.969189354659</v>
       </c>
     </row>
-    <row r="64" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I64">
         <f t="shared" si="5"/>
         <v>1620</v>
@@ -11549,7 +11615,7 @@
         <v>1619.9671956642878</v>
       </c>
     </row>
-    <row r="65" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I65">
         <f t="shared" si="5"/>
         <v>1670</v>
@@ -11579,7 +11645,7 @@
         <v>1669.9651394777134</v>
       </c>
     </row>
-    <row r="66" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I66">
         <f t="shared" si="5"/>
         <v>1720</v>
@@ -11609,7 +11675,7 @@
         <v>1719.9630207950531</v>
       </c>
     </row>
-    <row r="67" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I67">
         <f t="shared" si="5"/>
         <v>1770</v>
@@ -11639,7 +11705,7 @@
         <v>1769.9608396164233</v>
       </c>
     </row>
-    <row r="68" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I68">
         <f t="shared" si="5"/>
         <v>1820</v>
@@ -11669,7 +11735,7 @@
         <v>1819.9585959419423</v>
       </c>
     </row>
-    <row r="69" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I69">
         <f t="shared" si="5"/>
         <v>1870</v>
@@ -11699,7 +11765,7 @@
         <v>1869.9562897717265</v>
       </c>
     </row>
-    <row r="70" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I70">
         <f t="shared" si="5"/>
         <v>1920</v>
@@ -11729,7 +11795,7 @@
         <v>1919.9539211058936</v>
       </c>
     </row>
-    <row r="71" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I71">
         <f t="shared" si="5"/>
         <v>1970</v>
@@ -11759,7 +11825,7 @@
         <v>1969.9514899445601</v>
       </c>
     </row>
-    <row r="72" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I72">
         <f t="shared" si="5"/>
         <v>2020</v>
@@ -11789,7 +11855,7 @@
         <v>2019.9489962878436</v>
       </c>
     </row>
-    <row r="73" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I73">
         <f t="shared" si="5"/>
         <v>2070</v>
@@ -11819,7 +11885,7 @@
         <v>2069.9464401358614</v>
       </c>
     </row>
-    <row r="74" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I74">
         <f t="shared" si="5"/>
         <v>2120</v>
@@ -11849,7 +11915,7 @@
         <v>2119.9438214887305</v>
       </c>
     </row>
-    <row r="75" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I75">
         <f t="shared" si="5"/>
         <v>2170</v>
@@ -11879,7 +11945,7 @@
         <v>2169.9411403465683</v>
       </c>
     </row>
-    <row r="76" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I76">
         <f t="shared" si="5"/>
         <v>2220</v>
@@ -11909,7 +11975,7 @@
         <v>2219.9383967094914</v>
       </c>
     </row>
-    <row r="77" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I77">
         <f t="shared" si="5"/>
         <v>2270</v>
@@ -11939,7 +12005,7 @@
         <v>2269.9355905776174</v>
       </c>
     </row>
-    <row r="78" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I78">
         <f t="shared" si="5"/>
         <v>2320</v>
@@ -11969,7 +12035,7 @@
         <v>2319.9327219510637</v>
       </c>
     </row>
-    <row r="79" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I79">
         <f t="shared" si="5"/>
         <v>2370</v>
@@ -11999,7 +12065,7 @@
         <v>2369.9297908299468</v>
       </c>
     </row>
-    <row r="80" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I80">
         <f t="shared" si="5"/>
         <v>2420</v>
@@ -12029,7 +12095,7 @@
         <v>2419.9267972143844</v>
       </c>
     </row>
-    <row r="81" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I81">
         <f t="shared" si="5"/>
         <v>2470</v>
@@ -12059,7 +12125,7 @@
         <v>2469.9237411044933</v>
       </c>
     </row>
-    <row r="82" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I82">
         <f t="shared" si="5"/>
         <v>2520</v>
@@ -12089,7 +12155,7 @@
         <v>2519.9206225003913</v>
       </c>
     </row>
-    <row r="83" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I83">
         <f t="shared" si="5"/>
         <v>2570</v>
@@ -12119,7 +12185,7 @@
         <v>2569.917441402195</v>
       </c>
     </row>
-    <row r="84" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I84">
         <f t="shared" si="5"/>
         <v>2620</v>
@@ -12149,7 +12215,7 @@
         <v>2619.914197810022</v>
       </c>
     </row>
-    <row r="85" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I85">
         <f t="shared" si="5"/>
         <v>2670</v>
@@ -12179,7 +12245,7 @@
         <v>2669.9108917239887</v>
       </c>
     </row>
-    <row r="86" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I86">
         <f t="shared" si="5"/>
         <v>2720</v>
@@ -12209,7 +12275,7 @@
         <v>2719.907523144213</v>
       </c>
     </row>
-    <row r="87" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I87">
         <f t="shared" si="5"/>
         <v>2770</v>
@@ -12239,7 +12305,7 @@
         <v>2769.9040920708121</v>
       </c>
     </row>
-    <row r="88" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I88">
         <f t="shared" si="5"/>
         <v>2820</v>
@@ -12269,7 +12335,7 @@
         <v>2819.9005985039025</v>
       </c>
     </row>
-    <row r="89" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I89">
         <f t="shared" si="5"/>
         <v>2870</v>
@@ -12299,7 +12365,7 @@
         <v>2869.9485202984174</v>
       </c>
     </row>
-    <row r="90" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I90">
         <f t="shared" si="5"/>
         <v>2920</v>
@@ -12329,7 +12395,7 @@
         <v>2919.9467109725247</v>
       </c>
     </row>
-    <row r="91" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I91">
         <f t="shared" si="5"/>
         <v>2970</v>
@@ -12359,7 +12425,7 @@
         <v>2969.944870398343</v>
       </c>
     </row>
-    <row r="92" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I92">
         <f t="shared" si="5"/>
         <v>3020</v>
@@ -12389,7 +12455,7 @@
         <v>3019.942998575902</v>
       </c>
     </row>
-    <row r="93" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I93">
         <f t="shared" si="5"/>
         <v>3070</v>
@@ -12419,7 +12485,7 @@
         <v>3069.9410955052299</v>
       </c>
     </row>
-    <row r="94" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I94">
         <f t="shared" si="5"/>
         <v>3120</v>
@@ -12449,7 +12515,7 @@
         <v>3119.9391611863571</v>
       </c>
     </row>
-    <row r="95" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I95">
         <f t="shared" si="5"/>
         <v>3170</v>
@@ -12479,7 +12545,7 @@
         <v>3169.9371956193118</v>
       </c>
     </row>
-    <row r="96" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I96">
         <f t="shared" si="5"/>
         <v>3220</v>
@@ -12509,7 +12575,7 @@
         <v>3219.935198804124</v>
       </c>
     </row>
-    <row r="97" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I97">
         <f t="shared" si="5"/>
         <v>3270</v>
@@ -12539,7 +12605,7 @@
         <v>3269.9331707408232</v>
       </c>
     </row>
-    <row r="98" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I98">
         <f t="shared" ref="I98:I161" si="13">50+I97</f>
         <v>3320</v>
@@ -12569,7 +12635,7 @@
         <v>3319.9311114294378</v>
       </c>
     </row>
-    <row r="99" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I99">
         <f t="shared" si="13"/>
         <v>3370</v>
@@ -12599,7 +12665,7 @@
         <v>3369.9290208699977</v>
       </c>
     </row>
-    <row r="100" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I100">
         <f t="shared" si="13"/>
         <v>3420</v>
@@ -12629,7 +12695,7 @@
         <v>3419.9268990625328</v>
       </c>
     </row>
-    <row r="101" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I101">
         <f t="shared" si="13"/>
         <v>3470</v>
@@ -12659,7 +12725,7 @@
         <v>3469.924746007071</v>
       </c>
     </row>
-    <row r="102" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I102">
         <f t="shared" si="13"/>
         <v>3520</v>
@@ -12689,7 +12755,7 @@
         <v>3519.9225617036423</v>
       </c>
     </row>
-    <row r="103" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I103">
         <f t="shared" si="13"/>
         <v>3570</v>
@@ -12719,7 +12785,7 @@
         <v>3569.9203461522766</v>
       </c>
     </row>
-    <row r="104" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I104">
         <f t="shared" si="13"/>
         <v>3620</v>
@@ -12749,7 +12815,7 @@
         <v>3619.9180993530017</v>
       </c>
     </row>
-    <row r="105" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I105">
         <f t="shared" si="13"/>
         <v>3670</v>
@@ -12779,7 +12845,7 @@
         <v>3669.915821305849</v>
       </c>
     </row>
-    <row r="106" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I106">
         <f t="shared" si="13"/>
         <v>3720</v>
@@ -12809,7 +12875,7 @@
         <v>3719.9135120108458</v>
       </c>
     </row>
-    <row r="107" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I107">
         <f t="shared" si="13"/>
         <v>3770</v>
@@ -12839,7 +12905,7 @@
         <v>3769.9111714680221</v>
       </c>
     </row>
-    <row r="108" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I108">
         <f t="shared" si="13"/>
         <v>3820</v>
@@ -12869,7 +12935,7 @@
         <v>3819.9087996774078</v>
       </c>
     </row>
-    <row r="109" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I109">
         <f t="shared" si="13"/>
         <v>3870</v>
@@ -12899,7 +12965,7 @@
         <v>3869.9063966390313</v>
       </c>
     </row>
-    <row r="110" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I110">
         <f t="shared" si="13"/>
         <v>3920</v>
@@ -12929,7 +12995,7 @@
         <v>3919.903962352922</v>
       </c>
     </row>
-    <row r="111" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I111">
         <f t="shared" si="13"/>
         <v>3970</v>
@@ -12959,7 +13025,7 @@
         <v>3969.90149681911</v>
       </c>
     </row>
-    <row r="112" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I112">
         <f t="shared" si="13"/>
         <v>4020</v>
@@ -12989,7 +13055,7 @@
         <v>4019.8990000376243</v>
       </c>
     </row>
-    <row r="113" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I113">
         <f t="shared" si="13"/>
         <v>4070</v>
@@ -13019,7 +13085,7 @@
         <v>4069.8964720084932</v>
       </c>
     </row>
-    <row r="114" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I114">
         <f t="shared" si="13"/>
         <v>4120</v>
@@ -13049,7 +13115,7 @@
         <v>4119.8939127317472</v>
       </c>
     </row>
-    <row r="115" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I115">
         <f t="shared" si="13"/>
         <v>4170</v>
@@ -13079,7 +13145,7 @@
         <v>4169.8913222074152</v>
       </c>
     </row>
-    <row r="116" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I116">
         <f t="shared" si="13"/>
         <v>4220</v>
@@ -13109,7 +13175,7 @@
         <v>4219.8887004355265</v>
       </c>
     </row>
-    <row r="117" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I117">
         <f t="shared" si="13"/>
         <v>4270</v>
@@ -13139,7 +13205,7 @@
         <v>4269.8860474161092</v>
       </c>
     </row>
-    <row r="118" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I118">
         <f t="shared" si="13"/>
         <v>4320</v>
@@ -13169,7 +13235,7 @@
         <v>4319.8833631491952</v>
       </c>
     </row>
-    <row r="119" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I119">
         <f t="shared" si="13"/>
         <v>4370</v>
@@ -13199,7 +13265,7 @@
         <v>4369.8806476348118</v>
       </c>
     </row>
-    <row r="120" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I120">
         <f t="shared" si="13"/>
         <v>4420</v>
@@ -13229,7 +13295,7 @@
         <v>4419.8779008729889</v>
       </c>
     </row>
-    <row r="121" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I121">
         <f t="shared" si="13"/>
         <v>4470</v>
@@ -13259,7 +13325,7 @@
         <v>4469.8751228637548</v>
       </c>
     </row>
-    <row r="122" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I122">
         <f t="shared" si="13"/>
         <v>4520</v>
@@ -13289,7 +13355,7 @@
         <v>4519.8723136071403</v>
       </c>
     </row>
-    <row r="123" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I123">
         <f t="shared" si="13"/>
         <v>4570</v>
@@ -13319,7 +13385,7 @@
         <v>4569.8694731031737</v>
       </c>
     </row>
-    <row r="124" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I124">
         <f t="shared" si="13"/>
         <v>4620</v>
@@ -13349,7 +13415,7 @@
         <v>4619.8666013518859</v>
       </c>
     </row>
-    <row r="125" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I125">
         <f t="shared" si="13"/>
         <v>4670</v>
@@ -13379,7 +13445,7 @@
         <v>4669.8636983533042</v>
       </c>
     </row>
-    <row r="126" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I126">
         <f t="shared" si="13"/>
         <v>4720</v>
@@ -13409,7 +13475,7 @@
         <v>4719.8607641074586</v>
       </c>
     </row>
-    <row r="127" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I127">
         <f t="shared" si="13"/>
         <v>4770</v>
@@ -13439,7 +13505,7 @@
         <v>4769.8577986143782</v>
       </c>
     </row>
-    <row r="128" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I128">
         <f t="shared" si="13"/>
         <v>4820</v>
@@ -13469,7 +13535,7 @@
         <v>4819.8548018740939</v>
       </c>
     </row>
-    <row r="129" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I129">
         <f t="shared" si="13"/>
         <v>4870</v>
@@ -13499,7 +13565,7 @@
         <v>4869.8517738866331</v>
       </c>
     </row>
-    <row r="130" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I130">
         <f t="shared" si="13"/>
         <v>4920</v>
@@ -13529,7 +13595,7 @@
         <v>4919.8487146520247</v>
       </c>
     </row>
-    <row r="131" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I131">
         <f t="shared" si="13"/>
         <v>4970</v>
@@ -13559,7 +13625,7 @@
         <v>4969.8456241702988</v>
       </c>
     </row>
-    <row r="132" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I132">
         <f t="shared" si="13"/>
         <v>5020</v>
@@ -13589,7 +13655,7 @@
         <v>5019.8425024414864</v>
       </c>
     </row>
-    <row r="133" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I133">
         <f t="shared" si="13"/>
         <v>5070</v>
@@ -13619,7 +13685,7 @@
         <v>5069.8393494656139</v>
       </c>
     </row>
-    <row r="134" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I134">
         <f t="shared" si="13"/>
         <v>5120</v>
@@ -13649,7 +13715,7 @@
         <v>5119.836165242712</v>
       </c>
     </row>
-    <row r="135" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I135">
         <f t="shared" si="13"/>
         <v>5170</v>
@@ -13679,7 +13745,7 @@
         <v>5169.8329497728109</v>
       </c>
     </row>
-    <row r="136" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I136">
         <f t="shared" si="13"/>
         <v>5220</v>
@@ -13709,7 +13775,7 @@
         <v>5219.8297030559379</v>
       </c>
     </row>
-    <row r="137" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="137" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I137">
         <f t="shared" si="13"/>
         <v>5270</v>
@@ -13739,7 +13805,7 @@
         <v>5269.8264250921238</v>
       </c>
     </row>
-    <row r="138" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="138" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I138">
         <f t="shared" si="13"/>
         <v>5320</v>
@@ -13769,7 +13835,7 @@
         <v>5319.8231158813969</v>
       </c>
     </row>
-    <row r="139" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="139" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I139">
         <f t="shared" si="13"/>
         <v>5370</v>
@@ -13799,7 +13865,7 @@
         <v>5369.8197754237872</v>
       </c>
     </row>
-    <row r="140" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="140" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I140">
         <f t="shared" si="13"/>
         <v>5420</v>
@@ -13829,7 +13895,7 @@
         <v>5419.8164037193237</v>
       </c>
     </row>
-    <row r="141" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="141" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I141">
         <f t="shared" si="13"/>
         <v>5470</v>
@@ -13859,7 +13925,7 @@
         <v>5469.8130007680365</v>
       </c>
     </row>
-    <row r="142" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="142" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I142">
         <f t="shared" si="13"/>
         <v>5520</v>
@@ -13889,7 +13955,7 @@
         <v>5519.8095665699529</v>
       </c>
     </row>
-    <row r="143" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I143">
         <f t="shared" si="13"/>
         <v>5570</v>
@@ -13919,7 +13985,7 @@
         <v>5569.8061011251048</v>
       </c>
     </row>
-    <row r="144" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I144">
         <f t="shared" si="13"/>
         <v>5620</v>
@@ -13949,7 +14015,7 @@
         <v>5619.8026044335193</v>
       </c>
     </row>
-    <row r="145" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="145" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I145">
         <f t="shared" si="13"/>
         <v>5670</v>
@@ -13979,7 +14045,7 @@
         <v>5669.7990764952274</v>
       </c>
     </row>
-    <row r="146" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="146" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I146">
         <f t="shared" si="13"/>
         <v>5720</v>
@@ -14009,7 +14075,7 @@
         <v>5719.7955173102564</v>
       </c>
     </row>
-    <row r="147" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="147" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I147">
         <f t="shared" si="13"/>
         <v>5770</v>
@@ -14039,7 +14105,7 @@
         <v>5769.7919268786372</v>
       </c>
     </row>
-    <row r="148" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="148" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I148">
         <f t="shared" si="13"/>
         <v>5820</v>
@@ -14069,7 +14135,7 @@
         <v>5819.788305200399</v>
       </c>
     </row>
-    <row r="149" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="149" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I149">
         <f t="shared" si="13"/>
         <v>5870</v>
@@ -14099,7 +14165,7 @@
         <v>5869.7846522755699</v>
       </c>
     </row>
-    <row r="150" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="150" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I150">
         <f t="shared" si="13"/>
         <v>5920</v>
@@ -14129,7 +14195,7 @@
         <v>5919.7809681041799</v>
       </c>
     </row>
-    <row r="151" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="151" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I151">
         <f t="shared" si="13"/>
         <v>5970</v>
@@ -14159,7 +14225,7 @@
         <v>5969.7772526862591</v>
       </c>
     </row>
-    <row r="152" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="152" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I152">
         <f t="shared" si="13"/>
         <v>6020</v>
@@ -14189,7 +14255,7 @@
         <v>6019.7735060218356</v>
       </c>
     </row>
-    <row r="153" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="153" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I153">
         <f t="shared" si="13"/>
         <v>6070</v>
@@ -14219,7 +14285,7 @@
         <v>6069.7697281109404</v>
       </c>
     </row>
-    <row r="154" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="154" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I154">
         <f t="shared" si="13"/>
         <v>6120</v>
@@ -14249,7 +14315,7 @@
         <v>6119.7659189536007</v>
       </c>
     </row>
-    <row r="155" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="155" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I155">
         <f t="shared" si="13"/>
         <v>6170</v>
@@ -14279,7 +14345,7 @@
         <v>6169.7620785498466</v>
       </c>
     </row>
-    <row r="156" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="156" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I156">
         <f t="shared" si="13"/>
         <v>6220</v>
@@ -14309,7 +14375,7 @@
         <v>6219.7582068997071</v>
       </c>
     </row>
-    <row r="157" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I157">
         <f t="shared" si="13"/>
         <v>6270</v>
@@ -14339,7 +14405,7 @@
         <v>6269.7543040032115</v>
       </c>
     </row>
-    <row r="158" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I158">
         <f t="shared" si="13"/>
         <v>6320</v>
@@ -14369,7 +14435,7 @@
         <v>6319.7503698603905</v>
       </c>
     </row>
-    <row r="159" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I159">
         <f t="shared" si="13"/>
         <v>6370</v>
@@ -14399,7 +14465,7 @@
         <v>6369.7464044712724</v>
       </c>
     </row>
-    <row r="160" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I160">
         <f t="shared" si="13"/>
         <v>6420</v>
@@ -14429,7 +14495,7 @@
         <v>6419.7424078358863</v>
       </c>
     </row>
-    <row r="161" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I161">
         <f t="shared" si="13"/>
         <v>6470</v>
@@ -14459,7 +14525,7 @@
         <v>6469.7383799542604</v>
       </c>
     </row>
-    <row r="162" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I162">
         <f t="shared" ref="I162:I225" si="20">50+I161</f>
         <v>6520</v>
@@ -14489,7 +14555,7 @@
         <v>6519.7343208264265</v>
       </c>
     </row>
-    <row r="163" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I163">
         <f t="shared" si="20"/>
         <v>6570</v>
@@ -14519,7 +14585,7 @@
         <v>6569.7302304524128</v>
       </c>
     </row>
-    <row r="164" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I164">
         <f t="shared" si="20"/>
         <v>6620</v>
@@ -14549,7 +14615,7 @@
         <v>6619.7261088322475</v>
       </c>
     </row>
-    <row r="165" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I165">
         <f t="shared" si="20"/>
         <v>6670</v>
@@ -14579,7 +14645,7 @@
         <v>6669.7219559659607</v>
       </c>
     </row>
-    <row r="166" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I166">
         <f t="shared" si="20"/>
         <v>6720</v>
@@ -14609,7 +14675,7 @@
         <v>6719.7177718535822</v>
       </c>
     </row>
-    <row r="167" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I167">
         <f t="shared" si="20"/>
         <v>6770</v>
@@ -14639,7 +14705,7 @@
         <v>6769.7135564951404</v>
       </c>
     </row>
-    <row r="168" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I168">
         <f t="shared" si="20"/>
         <v>6820</v>
@@ -14669,7 +14735,7 @@
         <v>6819.7093098906662</v>
       </c>
     </row>
-    <row r="169" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I169">
         <f t="shared" si="20"/>
         <v>6870</v>
@@ -14699,7 +14765,7 @@
         <v>6869.7050320401868</v>
       </c>
     </row>
-    <row r="170" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I170">
         <f t="shared" si="20"/>
         <v>6920</v>
@@ -14729,7 +14795,7 @@
         <v>6919.7007229437331</v>
       </c>
     </row>
-    <row r="171" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I171">
         <f t="shared" si="20"/>
         <v>6970</v>
@@ -14759,7 +14825,7 @@
         <v>6969.6963826013325</v>
       </c>
     </row>
-    <row r="172" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I172">
         <f t="shared" si="20"/>
         <v>7020</v>
@@ -14789,7 +14855,7 @@
         <v>7019.6920110130168</v>
       </c>
     </row>
-    <row r="173" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I173">
         <f t="shared" si="20"/>
         <v>7070</v>
@@ -14819,7 +14885,7 @@
         <v>7069.6876081788141</v>
       </c>
     </row>
-    <row r="174" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I174">
         <f t="shared" si="20"/>
         <v>7120</v>
@@ -14849,7 +14915,7 @@
         <v>7119.6831740987527</v>
       </c>
     </row>
-    <row r="175" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I175">
         <f t="shared" si="20"/>
         <v>7170</v>
@@ -14879,7 +14945,7 @@
         <v>7169.6787087728635</v>
       </c>
     </row>
-    <row r="176" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I176">
         <f t="shared" si="20"/>
         <v>7220</v>
@@ -14909,7 +14975,7 @@
         <v>7219.6742122011738</v>
       </c>
     </row>
-    <row r="177" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I177">
         <f t="shared" si="20"/>
         <v>7270</v>
@@ -14939,7 +15005,7 @@
         <v>7269.6696843837153</v>
       </c>
     </row>
-    <row r="178" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I178">
         <f t="shared" si="20"/>
         <v>7320</v>
@@ -14969,7 +15035,7 @@
         <v>7319.6651253205173</v>
       </c>
     </row>
-    <row r="179" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I179">
         <f t="shared" si="20"/>
         <v>7370</v>
@@ -14999,7 +15065,7 @@
         <v>7369.6605350116051</v>
       </c>
     </row>
-    <row r="180" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I180">
         <f t="shared" si="20"/>
         <v>7420</v>
@@ -15029,7 +15095,7 @@
         <v>7419.6559134570134</v>
       </c>
     </row>
-    <row r="181" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I181">
         <f t="shared" si="20"/>
         <v>7470</v>
@@ -15059,7 +15125,7 @@
         <v>7469.6512606567685</v>
       </c>
     </row>
-    <row r="182" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I182">
         <f t="shared" si="20"/>
         <v>7520</v>
@@ -15089,7 +15155,7 @@
         <v>7519.6465766108995</v>
       </c>
     </row>
-    <row r="183" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I183">
         <f t="shared" si="20"/>
         <v>7570</v>
@@ -15119,7 +15185,7 @@
         <v>7569.6418613194364</v>
       </c>
     </row>
-    <row r="184" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I184">
         <f t="shared" si="20"/>
         <v>7620</v>
@@ -15149,7 +15215,7 @@
         <v>7619.6371147824093</v>
       </c>
     </row>
-    <row r="185" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I185">
         <f t="shared" si="20"/>
         <v>7670</v>
@@ -15179,7 +15245,7 @@
         <v>7669.6323369998454</v>
       </c>
     </row>
-    <row r="186" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I186">
         <f t="shared" si="20"/>
         <v>7720</v>
@@ -15209,7 +15275,7 @@
         <v>7719.6275279717756</v>
       </c>
     </row>
-    <row r="187" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I187">
         <f t="shared" si="20"/>
         <v>7770</v>
@@ -15239,7 +15305,7 @@
         <v>7769.6226876982291</v>
       </c>
     </row>
-    <row r="188" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I188">
         <f t="shared" si="20"/>
         <v>7820</v>
@@ -15269,7 +15335,7 @@
         <v>7819.6178161792341</v>
       </c>
     </row>
-    <row r="189" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I189">
         <f t="shared" si="20"/>
         <v>7870</v>
@@ -15299,7 +15365,7 @@
         <v>7869.6129134148214</v>
       </c>
     </row>
-    <row r="190" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I190">
         <f t="shared" si="20"/>
         <v>7920</v>
@@ -15329,7 +15395,7 @@
         <v>7919.6079794050193</v>
       </c>
     </row>
-    <row r="191" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I191">
         <f t="shared" si="20"/>
         <v>7970</v>
@@ -15359,7 +15425,7 @@
         <v>7969.6030141498577</v>
       </c>
     </row>
-    <row r="192" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I192">
         <f t="shared" si="20"/>
         <v>8020</v>
@@ -15389,7 +15455,7 @@
         <v>8019.5980176493649</v>
       </c>
     </row>
-    <row r="193" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I193">
         <f t="shared" si="20"/>
         <v>8070</v>
@@ -15419,7 +15485,7 @@
         <v>8069.5929899035727</v>
       </c>
     </row>
-    <row r="194" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I194">
         <f t="shared" si="20"/>
         <v>8120</v>
@@ -15449,7 +15515,7 @@
         <v>8119.5879309125066</v>
       </c>
     </row>
-    <row r="195" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I195">
         <f t="shared" si="20"/>
         <v>8170</v>
@@ -15479,7 +15545,7 @@
         <v>8169.5828406761975</v>
       </c>
     </row>
-    <row r="196" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I196">
         <f t="shared" si="20"/>
         <v>8220</v>
@@ -15509,7 +15575,7 @@
         <v>8219.5777191946763</v>
       </c>
     </row>
-    <row r="197" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I197">
         <f t="shared" si="20"/>
         <v>8270</v>
@@ -15539,7 +15605,7 @@
         <v>8269.5725664679703</v>
       </c>
     </row>
-    <row r="198" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I198">
         <f t="shared" si="20"/>
         <v>8320</v>
@@ -15569,7 +15635,7 @@
         <v>8319.5673824961104</v>
       </c>
     </row>
-    <row r="199" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I199">
         <f t="shared" si="20"/>
         <v>8370</v>
@@ -15599,7 +15665,7 @@
         <v>8369.562167279124</v>
       </c>
     </row>
-    <row r="200" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I200">
         <f t="shared" si="20"/>
         <v>8420</v>
@@ -15629,7 +15695,7 @@
         <v>8419.5569208170418</v>
       </c>
     </row>
-    <row r="201" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I201">
         <f t="shared" si="20"/>
         <v>8470</v>
@@ -15659,7 +15725,7 @@
         <v>8469.5516431098931</v>
       </c>
     </row>
-    <row r="202" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I202">
         <f t="shared" si="20"/>
         <v>8520</v>
@@ -15689,7 +15755,7 @@
         <v>8519.546334157707</v>
       </c>
     </row>
-    <row r="203" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I203">
         <f t="shared" si="20"/>
         <v>8570</v>
@@ -15719,7 +15785,7 @@
         <v>8569.5409939605106</v>
       </c>
     </row>
-    <row r="204" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I204">
         <f t="shared" si="20"/>
         <v>8620</v>
@@ -15749,7 +15815,7 @@
         <v>8619.5356225183368</v>
       </c>
     </row>
-    <row r="205" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I205">
         <f t="shared" si="20"/>
         <v>8670</v>
@@ -15779,7 +15845,7 @@
         <v>8669.5302198312129</v>
       </c>
     </row>
-    <row r="206" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I206">
         <f t="shared" si="20"/>
         <v>8720</v>
@@ -15809,7 +15875,7 @@
         <v>8719.5247858991697</v>
       </c>
     </row>
-    <row r="207" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I207">
         <f t="shared" si="20"/>
         <v>8770</v>
@@ -15839,7 +15905,7 @@
         <v>8769.5193207222328</v>
       </c>
     </row>
-    <row r="208" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I208">
         <f t="shared" si="20"/>
         <v>8820</v>
@@ -15869,7 +15935,7 @@
         <v>8819.5138243004349</v>
       </c>
     </row>
-    <row r="209" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I209">
         <f t="shared" si="20"/>
         <v>8870</v>
@@ -15899,7 +15965,7 @@
         <v>8869.508296633805</v>
       </c>
     </row>
-    <row r="210" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I210">
         <f t="shared" si="20"/>
         <v>8920</v>
@@ -15929,7 +15995,7 @@
         <v>8919.5027377223723</v>
       </c>
     </row>
-    <row r="211" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I211">
         <f t="shared" si="20"/>
         <v>8970</v>
@@ -15959,7 +16025,7 @@
         <v>8969.4971475661641</v>
       </c>
     </row>
-    <row r="212" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I212">
         <f t="shared" si="20"/>
         <v>9020</v>
@@ -15989,7 +16055,7 @@
         <v>9019.4915261652113</v>
       </c>
     </row>
-    <row r="213" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I213">
         <f t="shared" si="20"/>
         <v>9070</v>
@@ -16019,7 +16085,7 @@
         <v>9069.4858735195448</v>
       </c>
     </row>
-    <row r="214" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I214">
         <f t="shared" si="20"/>
         <v>9120</v>
@@ -16049,7 +16115,7 @@
         <v>9119.480189629192</v>
       </c>
     </row>
-    <row r="215" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I215">
         <f t="shared" si="20"/>
         <v>9170</v>
@@ -16079,7 +16145,7 @@
         <v>9169.47447449418</v>
       </c>
     </row>
-    <row r="216" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I216">
         <f t="shared" si="20"/>
         <v>9220</v>
@@ -16109,7 +16175,7 @@
         <v>9219.4687281145434</v>
       </c>
     </row>
-    <row r="217" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I217">
         <f t="shared" si="20"/>
         <v>9270</v>
@@ -16139,7 +16205,7 @@
         <v>9269.462950490306</v>
       </c>
     </row>
-    <row r="218" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I218">
         <f t="shared" si="20"/>
         <v>9320</v>
@@ -16169,7 +16235,7 @@
         <v>9319.4571416215003</v>
       </c>
     </row>
-    <row r="219" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I219">
         <f t="shared" si="20"/>
         <v>9370</v>
@@ -16199,7 +16265,7 @@
         <v>9369.4513015081538</v>
       </c>
     </row>
-    <row r="220" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I220">
         <f t="shared" si="20"/>
         <v>9420</v>
@@ -16229,7 +16295,7 @@
         <v>9419.4454301502992</v>
       </c>
     </row>
-    <row r="221" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I221">
         <f t="shared" si="20"/>
         <v>9470</v>
@@ -16259,7 +16325,7 @@
         <v>9469.4395275479637</v>
       </c>
     </row>
-    <row r="222" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I222">
         <f t="shared" si="20"/>
         <v>9520</v>
@@ -16289,7 +16355,7 @@
         <v>9519.4335937011747</v>
       </c>
     </row>
-    <row r="223" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I223">
         <f t="shared" si="20"/>
         <v>9570</v>
@@ -16319,7 +16385,7 @@
         <v>9569.4276286099648</v>
       </c>
     </row>
-    <row r="224" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I224">
         <f t="shared" si="20"/>
         <v>9620</v>
@@ -16349,7 +16415,7 @@
         <v>9619.4216322743596</v>
       </c>
     </row>
-    <row r="225" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I225">
         <f t="shared" si="20"/>
         <v>9670</v>
@@ -16379,7 +16445,7 @@
         <v>9669.4156046943899</v>
       </c>
     </row>
-    <row r="226" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I226">
         <f t="shared" ref="I226:I231" si="27">50+I225</f>
         <v>9720</v>
@@ -16409,7 +16475,7 @@
         <v>9719.4095458700867</v>
       </c>
     </row>
-    <row r="227" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I227">
         <f t="shared" si="27"/>
         <v>9770</v>
@@ -16439,7 +16505,7 @@
         <v>9769.403455801481</v>
       </c>
     </row>
-    <row r="228" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I228">
         <f t="shared" si="27"/>
         <v>9820</v>
@@ -16469,7 +16535,7 @@
         <v>9819.3973344885962</v>
       </c>
     </row>
-    <row r="229" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I229">
         <f t="shared" si="27"/>
         <v>9870</v>
@@ -16499,7 +16565,7 @@
         <v>9869.3911819314635</v>
       </c>
     </row>
-    <row r="230" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I230">
         <f t="shared" si="27"/>
         <v>9920</v>
@@ -16529,7 +16595,7 @@
         <v>9919.3849981301155</v>
       </c>
     </row>
-    <row r="231" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I231">
         <f t="shared" si="27"/>
         <v>9970</v>
@@ -16559,7 +16625,7 @@
         <v>9969.3787830845795</v>
       </c>
     </row>
-    <row r="232" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I232">
         <f>50+I231</f>
         <v>10020</v>
@@ -16589,7 +16655,7 @@
         <v>10019.372536794883</v>
       </c>
     </row>
-    <row r="233" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I233">
         <f t="shared" ref="I233:I254" si="29">50+I232</f>
         <v>10070</v>
@@ -16619,7 +16685,7 @@
         <v>10069.366259261058</v>
       </c>
     </row>
-    <row r="234" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I234">
         <f t="shared" si="29"/>
         <v>10120</v>
@@ -16649,7 +16715,7 @@
         <v>10119.359950483131</v>
       </c>
     </row>
-    <row r="235" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I235">
         <f t="shared" si="29"/>
         <v>10170</v>
@@ -16679,7 +16745,7 @@
         <v>10169.353610461136</v>
       </c>
     </row>
-    <row r="236" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I236">
         <f t="shared" si="29"/>
         <v>10220</v>
@@ -16709,7 +16775,7 @@
         <v>10219.347239195096</v>
       </c>
     </row>
-    <row r="237" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I237">
         <f t="shared" si="29"/>
         <v>10270</v>
@@ -16739,7 +16805,7 @@
         <v>10269.340836685045</v>
       </c>
     </row>
-    <row r="238" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I238">
         <f t="shared" si="29"/>
         <v>10320</v>
@@ -16769,7 +16835,7 @@
         <v>10319.33440293101</v>
       </c>
     </row>
-    <row r="239" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I239">
         <f t="shared" si="29"/>
         <v>10370</v>
@@ -16799,7 +16865,7 @@
         <v>10369.327937933023</v>
       </c>
     </row>
-    <row r="240" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I240">
         <f t="shared" si="29"/>
         <v>10420</v>
@@ -16829,7 +16895,7 @@
         <v>10419.321441691109</v>
       </c>
     </row>
-    <row r="241" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I241">
         <f t="shared" si="29"/>
         <v>10470</v>
@@ -16859,7 +16925,7 @@
         <v>10469.314914205301</v>
       </c>
     </row>
-    <row r="242" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I242">
         <f t="shared" si="29"/>
         <v>10520</v>
@@ -16889,7 +16955,7 @@
         <v>10519.308355475627</v>
       </c>
     </row>
-    <row r="243" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I243">
         <f t="shared" si="29"/>
         <v>10570</v>
@@ -16919,7 +16985,7 @@
         <v>10569.301765502116</v>
       </c>
     </row>
-    <row r="244" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I244">
         <f t="shared" si="29"/>
         <v>10620</v>
@@ -16949,7 +17015,7 @@
         <v>10619.295144284799</v>
       </c>
     </row>
-    <row r="245" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I245">
         <f t="shared" si="29"/>
         <v>10670</v>
@@ -16979,7 +17045,7 @@
         <v>10669.288491823701</v>
       </c>
     </row>
-    <row r="246" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I246">
         <f t="shared" si="29"/>
         <v>10720</v>
@@ -17009,7 +17075,7 @@
         <v>10719.281808118856</v>
       </c>
     </row>
-    <row r="247" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I247">
         <f t="shared" si="29"/>
         <v>10770</v>
@@ -17039,7 +17105,7 @@
         <v>10769.275093170292</v>
       </c>
     </row>
-    <row r="248" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I248">
         <f t="shared" si="29"/>
         <v>10820</v>
@@ -17069,7 +17135,7 @@
         <v>10819.268346978037</v>
       </c>
     </row>
-    <row r="249" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I249">
         <f t="shared" si="29"/>
         <v>10870</v>
@@ -17099,7 +17165,7 @@
         <v>10869.261569542119</v>
       </c>
     </row>
-    <row r="250" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I250">
         <f t="shared" si="29"/>
         <v>10920</v>
@@ -17129,7 +17195,7 @@
         <v>10919.254760862572</v>
       </c>
     </row>
-    <row r="251" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I251">
         <f t="shared" si="29"/>
         <v>10970</v>
@@ -17159,7 +17225,7 @@
         <v>10969.247920939421</v>
       </c>
     </row>
-    <row r="252" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I252">
         <f t="shared" si="29"/>
         <v>11020</v>
@@ -17189,7 +17255,7 @@
         <v>11019.241049772698</v>
       </c>
     </row>
-    <row r="253" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I253">
         <f t="shared" si="29"/>
         <v>11070</v>
@@ -17219,7 +17285,7 @@
         <v>11069.234147362429</v>
       </c>
     </row>
-    <row r="254" spans="9:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I254">
         <f t="shared" si="29"/>
         <v>11120</v>
